--- a/orchavate_gtm_workflow/outputs/v1.1_nse_tracker_enriched_clearbit_20260806_193605_attempt1_succesful_reviewnotdone_orchavatecore_digital/Simple_Accessibility_Outreach_Tracker_v13_SemiFinal.xlsx
+++ b/orchavate_gtm_workflow/outputs/v1.1_nse_tracker_enriched_clearbit_20260806_193605_attempt1_succesful_reviewnotdone_orchavatecore_digital/Simple_Accessibility_Outreach_Tracker_v13_SemiFinal.xlsx
@@ -475,10 +475,10 @@
         <v>No</v>
       </c>
       <c r="H2" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I2">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="J2">
         <v>30</v>
@@ -528,10 +528,10 @@
         <v>No</v>
       </c>
       <c r="H3" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.5 out of 10</v>
       </c>
       <c r="I3">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="J3">
         <v>30</v>
@@ -581,10 +581,10 @@
         <v>No</v>
       </c>
       <c r="H4" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.1 out of 10</v>
       </c>
       <c r="I4">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J4">
         <v>30</v>
@@ -634,10 +634,10 @@
         <v>No</v>
       </c>
       <c r="H5" t="str">
-        <v>6.5 out of 10</v>
+        <v>2 out of 10</v>
       </c>
       <c r="I5">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="J5">
         <v>30</v>
@@ -687,10 +687,10 @@
         <v>No</v>
       </c>
       <c r="H6" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I6">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="J6">
         <v>30</v>
@@ -740,10 +740,10 @@
         <v>No</v>
       </c>
       <c r="H7" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.3 out of 10</v>
       </c>
       <c r="I7">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J7">
         <v>30</v>
@@ -793,10 +793,10 @@
         <v>No</v>
       </c>
       <c r="H8" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.1 out of 10</v>
       </c>
       <c r="I8">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J8">
         <v>30</v>
@@ -846,10 +846,10 @@
         <v>No</v>
       </c>
       <c r="H9" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.4 out of 10</v>
       </c>
       <c r="I9">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="J9">
         <v>30</v>
@@ -899,10 +899,10 @@
         <v>No</v>
       </c>
       <c r="H10" t="str">
-        <v>6.5 out of 10</v>
+        <v>5 out of 10</v>
       </c>
       <c r="I10">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J10">
         <v>30</v>
@@ -952,10 +952,10 @@
         <v>No</v>
       </c>
       <c r="H11" t="str">
-        <v>6.5 out of 10</v>
+        <v>6 out of 10</v>
       </c>
       <c r="I11">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J11">
         <v>30</v>
@@ -1005,10 +1005,10 @@
         <v>No</v>
       </c>
       <c r="H12" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.2 out of 10</v>
       </c>
       <c r="I12">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="J12">
         <v>30</v>
@@ -1058,10 +1058,10 @@
         <v>No</v>
       </c>
       <c r="H13" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.1 out of 10</v>
       </c>
       <c r="I13">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J13">
         <v>30</v>
@@ -1111,10 +1111,10 @@
         <v>No</v>
       </c>
       <c r="H14" t="str">
-        <v>6.5 out of 10</v>
+        <v>6 out of 10</v>
       </c>
       <c r="I14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J14">
         <v>30</v>
@@ -1164,10 +1164,10 @@
         <v>No</v>
       </c>
       <c r="H15" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.8 out of 10</v>
       </c>
       <c r="I15">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="J15">
         <v>30</v>
@@ -1217,10 +1217,10 @@
         <v>No</v>
       </c>
       <c r="H16" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.2 out of 10</v>
       </c>
       <c r="I16">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J16">
         <v>30</v>
@@ -1270,10 +1270,10 @@
         <v>No</v>
       </c>
       <c r="H17" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.3 out of 10</v>
       </c>
       <c r="I17">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="J17">
         <v>30</v>
@@ -1323,10 +1323,10 @@
         <v>No</v>
       </c>
       <c r="H18" t="str">
-        <v>6.5 out of 10</v>
+        <v>6 out of 10</v>
       </c>
       <c r="I18">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J18">
         <v>30</v>
@@ -1376,10 +1376,10 @@
         <v>No</v>
       </c>
       <c r="H19" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.2 out of 10</v>
       </c>
       <c r="I19">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="J19">
         <v>30</v>
@@ -1429,10 +1429,10 @@
         <v>No</v>
       </c>
       <c r="H20" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.4 out of 10</v>
       </c>
       <c r="I20">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J20">
         <v>30</v>
@@ -1482,10 +1482,10 @@
         <v>No</v>
       </c>
       <c r="H21" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.8 out of 10</v>
       </c>
       <c r="I21">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J21">
         <v>30</v>
@@ -1535,10 +1535,10 @@
         <v>No</v>
       </c>
       <c r="H22" t="str">
-        <v>6.5 out of 10</v>
+        <v>2 out of 10</v>
       </c>
       <c r="I22">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="J22">
         <v>30</v>
@@ -1588,10 +1588,10 @@
         <v>No</v>
       </c>
       <c r="H23" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I23">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="J23">
         <v>30</v>
@@ -1641,10 +1641,10 @@
         <v>No</v>
       </c>
       <c r="H24" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.1 out of 10</v>
       </c>
       <c r="I24">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="J24">
         <v>30</v>
@@ -1694,10 +1694,10 @@
         <v>No</v>
       </c>
       <c r="H25" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.6 out of 10</v>
       </c>
       <c r="I25">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J25">
         <v>30</v>
@@ -1747,10 +1747,10 @@
         <v>No</v>
       </c>
       <c r="H26" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.5 out of 10</v>
       </c>
       <c r="I26">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J26">
         <v>30</v>
@@ -1800,10 +1800,10 @@
         <v>No</v>
       </c>
       <c r="H27" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.7 out of 10</v>
       </c>
       <c r="I27">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J27">
         <v>30</v>
@@ -1853,10 +1853,10 @@
         <v>No</v>
       </c>
       <c r="H28" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I28">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="J28">
         <v>30</v>
@@ -1906,10 +1906,10 @@
         <v>No</v>
       </c>
       <c r="H29" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.6 out of 10</v>
       </c>
       <c r="I29">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J29">
         <v>30</v>
@@ -1959,10 +1959,10 @@
         <v>No</v>
       </c>
       <c r="H30" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.6 out of 10</v>
       </c>
       <c r="I30">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J30">
         <v>30</v>
@@ -2012,10 +2012,10 @@
         <v>No</v>
       </c>
       <c r="H31" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.5 out of 10</v>
       </c>
       <c r="I31">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="J31">
         <v>30</v>
@@ -2065,10 +2065,10 @@
         <v>No</v>
       </c>
       <c r="H32" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I32">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="J32">
         <v>30</v>
@@ -2118,10 +2118,10 @@
         <v>No</v>
       </c>
       <c r="H33" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.8 out of 10</v>
       </c>
       <c r="I33">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="J33">
         <v>30</v>
@@ -2171,10 +2171,10 @@
         <v>No</v>
       </c>
       <c r="H34" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.8 out of 10</v>
       </c>
       <c r="I34">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J34">
         <v>30</v>
@@ -2224,10 +2224,10 @@
         <v>No</v>
       </c>
       <c r="H35" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.5 out of 10</v>
       </c>
       <c r="I35">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J35">
         <v>30</v>
@@ -2277,10 +2277,10 @@
         <v>No</v>
       </c>
       <c r="H36" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.2 out of 10</v>
       </c>
       <c r="I36">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="J36">
         <v>30</v>
@@ -2330,10 +2330,10 @@
         <v>No</v>
       </c>
       <c r="H37" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I37">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="J37">
         <v>30</v>
@@ -2383,10 +2383,10 @@
         <v>No</v>
       </c>
       <c r="H38" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.4 out of 10</v>
       </c>
       <c r="I38">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J38">
         <v>30</v>
@@ -2436,10 +2436,10 @@
         <v>No</v>
       </c>
       <c r="H39" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.4 out of 10</v>
       </c>
       <c r="I39">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J39">
         <v>30</v>
@@ -2489,10 +2489,10 @@
         <v>No</v>
       </c>
       <c r="H40" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.4 out of 10</v>
       </c>
       <c r="I40">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J40">
         <v>30</v>
@@ -2542,10 +2542,10 @@
         <v>No</v>
       </c>
       <c r="H41" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.6 out of 10</v>
       </c>
       <c r="I41">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J41">
         <v>30</v>
@@ -2595,10 +2595,10 @@
         <v>No</v>
       </c>
       <c r="H42" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I42">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="J42">
         <v>30</v>
@@ -2648,10 +2648,10 @@
         <v>No</v>
       </c>
       <c r="H43" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.2 out of 10</v>
       </c>
       <c r="I43">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J43">
         <v>30</v>
@@ -2701,10 +2701,10 @@
         <v>No</v>
       </c>
       <c r="H44" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.1 out of 10</v>
       </c>
       <c r="I44">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="J44">
         <v>30</v>
@@ -2754,10 +2754,10 @@
         <v>No</v>
       </c>
       <c r="H45" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I45">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="J45">
         <v>30</v>
@@ -2807,10 +2807,10 @@
         <v>No</v>
       </c>
       <c r="H46" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.8 out of 10</v>
       </c>
       <c r="I46">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J46">
         <v>30</v>
@@ -2860,10 +2860,10 @@
         <v>No</v>
       </c>
       <c r="H47" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I47">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="J47">
         <v>30</v>
@@ -2913,10 +2913,10 @@
         <v>No</v>
       </c>
       <c r="H48" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I48">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="J48">
         <v>30</v>
@@ -2966,10 +2966,10 @@
         <v>No</v>
       </c>
       <c r="H49" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.6 out of 10</v>
       </c>
       <c r="I49">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J49">
         <v>30</v>
@@ -3019,10 +3019,10 @@
         <v>No</v>
       </c>
       <c r="H50" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.3 out of 10</v>
       </c>
       <c r="I50">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="J50">
         <v>30</v>
@@ -3072,10 +3072,10 @@
         <v>No</v>
       </c>
       <c r="H51" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I51">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="J51">
         <v>30</v>
@@ -3125,10 +3125,10 @@
         <v>No</v>
       </c>
       <c r="H52" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.1 out of 10</v>
       </c>
       <c r="I52">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J52">
         <v>30</v>
@@ -3178,10 +3178,10 @@
         <v>No</v>
       </c>
       <c r="H53" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.4 out of 10</v>
       </c>
       <c r="I53">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="J53">
         <v>30</v>
@@ -3231,10 +3231,10 @@
         <v>No</v>
       </c>
       <c r="H54" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.5 out of 10</v>
       </c>
       <c r="I54">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J54">
         <v>30</v>
@@ -3284,10 +3284,10 @@
         <v>No</v>
       </c>
       <c r="H55" t="str">
-        <v>6.5 out of 10</v>
+        <v>7 out of 10</v>
       </c>
       <c r="I55">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J55">
         <v>30</v>
@@ -3337,10 +3337,10 @@
         <v>No</v>
       </c>
       <c r="H56" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.4 out of 10</v>
       </c>
       <c r="I56">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J56">
         <v>30</v>
@@ -3443,10 +3443,10 @@
         <v>No</v>
       </c>
       <c r="H58" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I58">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="J58">
         <v>30</v>
@@ -3496,10 +3496,10 @@
         <v>No</v>
       </c>
       <c r="H59" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I59">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="J59">
         <v>30</v>
@@ -3549,10 +3549,10 @@
         <v>No</v>
       </c>
       <c r="H60" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.8 out of 10</v>
       </c>
       <c r="I60">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="J60">
         <v>30</v>
@@ -3655,10 +3655,10 @@
         <v>No</v>
       </c>
       <c r="H62" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.7 out of 10</v>
       </c>
       <c r="I62">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J62">
         <v>30</v>
@@ -3708,10 +3708,10 @@
         <v>No</v>
       </c>
       <c r="H63" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.3 out of 10</v>
       </c>
       <c r="I63">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J63">
         <v>30</v>
@@ -3761,10 +3761,10 @@
         <v>No</v>
       </c>
       <c r="H64" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.4 out of 10</v>
       </c>
       <c r="I64">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J64">
         <v>30</v>
@@ -3814,10 +3814,10 @@
         <v>No</v>
       </c>
       <c r="H65" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.2 out of 10</v>
       </c>
       <c r="I65">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J65">
         <v>30</v>
@@ -3867,10 +3867,10 @@
         <v>No</v>
       </c>
       <c r="H66" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.2 out of 10</v>
       </c>
       <c r="I66">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J66">
         <v>30</v>
@@ -3920,10 +3920,10 @@
         <v>No</v>
       </c>
       <c r="H67" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.8 out of 10</v>
       </c>
       <c r="I67">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J67">
         <v>30</v>
@@ -3973,10 +3973,10 @@
         <v>No</v>
       </c>
       <c r="H68" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.1 out of 10</v>
       </c>
       <c r="I68">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J68">
         <v>30</v>
@@ -4026,10 +4026,10 @@
         <v>No</v>
       </c>
       <c r="H69" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.9 out of 10</v>
       </c>
       <c r="I69">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J69">
         <v>30</v>
@@ -4079,10 +4079,10 @@
         <v>No</v>
       </c>
       <c r="H70" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.4 out of 10</v>
       </c>
       <c r="I70">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="J70">
         <v>30</v>
@@ -4132,10 +4132,10 @@
         <v>No</v>
       </c>
       <c r="H71" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I71">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J71">
         <v>30</v>
@@ -4185,10 +4185,10 @@
         <v>No</v>
       </c>
       <c r="H72" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I72">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="J72">
         <v>30</v>
@@ -4238,10 +4238,10 @@
         <v>No</v>
       </c>
       <c r="H73" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.3 out of 10</v>
       </c>
       <c r="I73">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J73">
         <v>30</v>
@@ -4291,10 +4291,10 @@
         <v>No</v>
       </c>
       <c r="H74" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I74">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="J74">
         <v>30</v>
@@ -4344,10 +4344,10 @@
         <v>No</v>
       </c>
       <c r="H75" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.8 out of 10</v>
       </c>
       <c r="I75">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="J75">
         <v>30</v>
@@ -4397,10 +4397,10 @@
         <v>No</v>
       </c>
       <c r="H76" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.6 out of 10</v>
       </c>
       <c r="I76">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J76">
         <v>30</v>
@@ -4450,10 +4450,10 @@
         <v>No</v>
       </c>
       <c r="H77" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.8 out of 10</v>
       </c>
       <c r="I77">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J77">
         <v>30</v>
@@ -4503,10 +4503,10 @@
         <v>No</v>
       </c>
       <c r="H78" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.3 out of 10</v>
       </c>
       <c r="I78">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J78">
         <v>30</v>
@@ -4556,10 +4556,10 @@
         <v>No</v>
       </c>
       <c r="H79" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.5 out of 10</v>
       </c>
       <c r="I79">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J79">
         <v>30</v>
@@ -4609,10 +4609,10 @@
         <v>No</v>
       </c>
       <c r="H80" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.5 out of 10</v>
       </c>
       <c r="I80">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J80">
         <v>30</v>
@@ -4662,10 +4662,10 @@
         <v>No</v>
       </c>
       <c r="H81" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.4 out of 10</v>
       </c>
       <c r="I81">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J81">
         <v>30</v>
@@ -4715,10 +4715,10 @@
         <v>No</v>
       </c>
       <c r="H82" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.8 out of 10</v>
       </c>
       <c r="I82">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J82">
         <v>30</v>
@@ -4768,10 +4768,10 @@
         <v>No</v>
       </c>
       <c r="H83" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.4 out of 10</v>
       </c>
       <c r="I83">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J83">
         <v>30</v>
@@ -4821,10 +4821,10 @@
         <v>No</v>
       </c>
       <c r="H84" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.6 out of 10</v>
       </c>
       <c r="I84">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J84">
         <v>30</v>
@@ -4874,10 +4874,10 @@
         <v>No</v>
       </c>
       <c r="H85" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.6 out of 10</v>
       </c>
       <c r="I85">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J85">
         <v>30</v>
@@ -4927,10 +4927,10 @@
         <v>No</v>
       </c>
       <c r="H86" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I86">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="J86">
         <v>30</v>
@@ -4980,10 +4980,10 @@
         <v>No</v>
       </c>
       <c r="H87" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.1 out of 10</v>
       </c>
       <c r="I87">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J87">
         <v>30</v>
@@ -5033,10 +5033,10 @@
         <v>No</v>
       </c>
       <c r="H88" t="str">
-        <v>6.5 out of 10</v>
+        <v>6 out of 10</v>
       </c>
       <c r="I88">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J88">
         <v>30</v>
@@ -5086,10 +5086,10 @@
         <v>No</v>
       </c>
       <c r="H89" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.6 out of 10</v>
       </c>
       <c r="I89">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J89">
         <v>30</v>
@@ -5139,10 +5139,10 @@
         <v>No</v>
       </c>
       <c r="H90" t="str">
-        <v>6.5 out of 10</v>
+        <v>3 out of 10</v>
       </c>
       <c r="I90">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="J90">
         <v>30</v>
@@ -5192,10 +5192,10 @@
         <v>No</v>
       </c>
       <c r="H91" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.5 out of 10</v>
       </c>
       <c r="I91">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="J91">
         <v>30</v>
@@ -5245,10 +5245,10 @@
         <v>No</v>
       </c>
       <c r="H92" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.7 out of 10</v>
       </c>
       <c r="I92">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J92">
         <v>30</v>
@@ -5298,10 +5298,10 @@
         <v>No</v>
       </c>
       <c r="H93" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.2 out of 10</v>
       </c>
       <c r="I93">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="J93">
         <v>30</v>
@@ -5404,10 +5404,10 @@
         <v>No</v>
       </c>
       <c r="H95" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.9 out of 10</v>
       </c>
       <c r="I95">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J95">
         <v>30</v>
@@ -5457,10 +5457,10 @@
         <v>No</v>
       </c>
       <c r="H96" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.2 out of 10</v>
       </c>
       <c r="I96">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J96">
         <v>30</v>
@@ -5510,10 +5510,10 @@
         <v>No</v>
       </c>
       <c r="H97" t="str">
-        <v>6.5 out of 10</v>
+        <v>3 out of 10</v>
       </c>
       <c r="I97">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="J97">
         <v>30</v>
@@ -5563,10 +5563,10 @@
         <v>No</v>
       </c>
       <c r="H98" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.4 out of 10</v>
       </c>
       <c r="I98">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J98">
         <v>30</v>
@@ -5616,10 +5616,10 @@
         <v>No</v>
       </c>
       <c r="H99" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.5 out of 10</v>
       </c>
       <c r="I99">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J99">
         <v>30</v>
@@ -5669,10 +5669,10 @@
         <v>No</v>
       </c>
       <c r="H100" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.3 out of 10</v>
       </c>
       <c r="I100">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J100">
         <v>30</v>
@@ -5722,10 +5722,10 @@
         <v>No</v>
       </c>
       <c r="H101" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.6 out of 10</v>
       </c>
       <c r="I101">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J101">
         <v>30</v>
@@ -5775,10 +5775,10 @@
         <v>No</v>
       </c>
       <c r="H102" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I102">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="J102">
         <v>30</v>
@@ -5828,10 +5828,10 @@
         <v>No</v>
       </c>
       <c r="H103" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.2 out of 10</v>
       </c>
       <c r="I103">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J103">
         <v>30</v>
@@ -5881,10 +5881,10 @@
         <v>No</v>
       </c>
       <c r="H104" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I104">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="J104">
         <v>30</v>
@@ -5934,10 +5934,10 @@
         <v>No</v>
       </c>
       <c r="H105" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I105">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="J105">
         <v>30</v>
@@ -5987,10 +5987,10 @@
         <v>No</v>
       </c>
       <c r="H106" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.9 out of 10</v>
       </c>
       <c r="I106">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J106">
         <v>30</v>
@@ -6040,10 +6040,10 @@
         <v>No</v>
       </c>
       <c r="H107" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.8 out of 10</v>
       </c>
       <c r="I107">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J107">
         <v>30</v>
@@ -6093,10 +6093,10 @@
         <v>No</v>
       </c>
       <c r="H108" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.8 out of 10</v>
       </c>
       <c r="I108">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="J108">
         <v>30</v>
@@ -6146,10 +6146,10 @@
         <v>No</v>
       </c>
       <c r="H109" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I109">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="J109">
         <v>30</v>
@@ -6199,10 +6199,10 @@
         <v>No</v>
       </c>
       <c r="H110" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.1 out of 10</v>
       </c>
       <c r="I110">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="J110">
         <v>30</v>
@@ -6252,10 +6252,10 @@
         <v>No</v>
       </c>
       <c r="H111" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.5 out of 10</v>
       </c>
       <c r="I111">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J111">
         <v>30</v>
@@ -6305,10 +6305,10 @@
         <v>No</v>
       </c>
       <c r="H112" t="str">
-        <v>6.5 out of 10</v>
+        <v>5 out of 10</v>
       </c>
       <c r="I112">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J112">
         <v>30</v>
@@ -6358,10 +6358,10 @@
         <v>No</v>
       </c>
       <c r="H113" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I113">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="J113">
         <v>30</v>
@@ -6411,10 +6411,10 @@
         <v>No</v>
       </c>
       <c r="H114" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.1 out of 10</v>
       </c>
       <c r="I114">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J114">
         <v>30</v>
@@ -6464,10 +6464,10 @@
         <v>No</v>
       </c>
       <c r="H115" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I115">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="J115">
         <v>30</v>
@@ -6517,10 +6517,10 @@
         <v>No</v>
       </c>
       <c r="H116" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I116">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="J116">
         <v>30</v>
@@ -6570,10 +6570,10 @@
         <v>No</v>
       </c>
       <c r="H117" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.3 out of 10</v>
       </c>
       <c r="I117">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="J117">
         <v>30</v>
@@ -6623,10 +6623,10 @@
         <v>No</v>
       </c>
       <c r="H118" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.6 out of 10</v>
       </c>
       <c r="I118">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J118">
         <v>30</v>
@@ -6676,10 +6676,10 @@
         <v>No</v>
       </c>
       <c r="H119" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.4 out of 10</v>
       </c>
       <c r="I119">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J119">
         <v>30</v>
@@ -6729,10 +6729,10 @@
         <v>No</v>
       </c>
       <c r="H120" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I120">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J120">
         <v>30</v>
@@ -6782,10 +6782,10 @@
         <v>No</v>
       </c>
       <c r="H121" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.1 out of 10</v>
       </c>
       <c r="I121">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J121">
         <v>30</v>
@@ -6835,10 +6835,10 @@
         <v>No</v>
       </c>
       <c r="H122" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.8 out of 10</v>
       </c>
       <c r="I122">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="J122">
         <v>30</v>
@@ -6888,10 +6888,10 @@
         <v>No</v>
       </c>
       <c r="H123" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.8 out of 10</v>
       </c>
       <c r="I123">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="J123">
         <v>30</v>
@@ -6941,10 +6941,10 @@
         <v>No</v>
       </c>
       <c r="H124" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.4 out of 10</v>
       </c>
       <c r="I124">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="J124">
         <v>30</v>
@@ -6994,10 +6994,10 @@
         <v>No</v>
       </c>
       <c r="H125" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I125">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="J125">
         <v>30</v>
@@ -7047,10 +7047,10 @@
         <v>No</v>
       </c>
       <c r="H126" t="str">
-        <v>6.5 out of 10</v>
+        <v>5 out of 10</v>
       </c>
       <c r="I126">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J126">
         <v>30</v>
@@ -7100,10 +7100,10 @@
         <v>No</v>
       </c>
       <c r="H127" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.1 out of 10</v>
       </c>
       <c r="I127">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J127">
         <v>30</v>
@@ -7153,10 +7153,10 @@
         <v>No</v>
       </c>
       <c r="H128" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.6 out of 10</v>
       </c>
       <c r="I128">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="J128">
         <v>30</v>
@@ -7206,10 +7206,10 @@
         <v>No</v>
       </c>
       <c r="H129" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.4 out of 10</v>
       </c>
       <c r="I129">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="J129">
         <v>30</v>
@@ -7259,10 +7259,10 @@
         <v>No</v>
       </c>
       <c r="H130" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.9 out of 10</v>
       </c>
       <c r="I130">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J130">
         <v>30</v>
@@ -7312,10 +7312,10 @@
         <v>No</v>
       </c>
       <c r="H131" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.2 out of 10</v>
       </c>
       <c r="I131">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J131">
         <v>30</v>
@@ -7365,10 +7365,10 @@
         <v>No</v>
       </c>
       <c r="H132" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I132">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="J132">
         <v>30</v>
@@ -7418,10 +7418,10 @@
         <v>No</v>
       </c>
       <c r="H133" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.6 out of 10</v>
       </c>
       <c r="I133">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J133">
         <v>30</v>
@@ -7471,10 +7471,10 @@
         <v>No</v>
       </c>
       <c r="H134" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.8 out of 10</v>
       </c>
       <c r="I134">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J134">
         <v>30</v>
@@ -7524,10 +7524,10 @@
         <v>No</v>
       </c>
       <c r="H135" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.4 out of 10</v>
       </c>
       <c r="I135">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J135">
         <v>30</v>
@@ -7577,10 +7577,10 @@
         <v>No</v>
       </c>
       <c r="H136" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.3 out of 10</v>
       </c>
       <c r="I136">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J136">
         <v>30</v>
@@ -7630,10 +7630,10 @@
         <v>No</v>
       </c>
       <c r="H137" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I137">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J137">
         <v>30</v>
@@ -7683,10 +7683,10 @@
         <v>No</v>
       </c>
       <c r="H138" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.9 out of 10</v>
       </c>
       <c r="I138">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J138">
         <v>30</v>
@@ -7736,10 +7736,10 @@
         <v>No</v>
       </c>
       <c r="H139" t="str">
-        <v>6.5 out of 10</v>
+        <v>3 out of 10</v>
       </c>
       <c r="I139">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="J139">
         <v>30</v>
@@ -7789,10 +7789,10 @@
         <v>No</v>
       </c>
       <c r="H140" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.3 out of 10</v>
       </c>
       <c r="I140">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J140">
         <v>30</v>
@@ -7842,10 +7842,10 @@
         <v>No</v>
       </c>
       <c r="H141" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I141">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="J141">
         <v>30</v>
@@ -7895,10 +7895,10 @@
         <v>No</v>
       </c>
       <c r="H142" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.3 out of 10</v>
       </c>
       <c r="I142">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J142">
         <v>30</v>
@@ -7948,10 +7948,10 @@
         <v>No</v>
       </c>
       <c r="H143" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I143">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="J143">
         <v>30</v>
@@ -8001,10 +8001,10 @@
         <v>No</v>
       </c>
       <c r="H144" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I144">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="J144">
         <v>30</v>
@@ -8054,10 +8054,10 @@
         <v>No</v>
       </c>
       <c r="H145" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.1 out of 10</v>
       </c>
       <c r="I145">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J145">
         <v>30</v>
@@ -8107,10 +8107,10 @@
         <v>No</v>
       </c>
       <c r="H146" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.8 out of 10</v>
       </c>
       <c r="I146">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J146">
         <v>30</v>
@@ -8160,10 +8160,10 @@
         <v>No</v>
       </c>
       <c r="H147" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.4 out of 10</v>
       </c>
       <c r="I147">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="J147">
         <v>30</v>
@@ -8213,10 +8213,10 @@
         <v>No</v>
       </c>
       <c r="H148" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.2 out of 10</v>
       </c>
       <c r="I148">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J148">
         <v>30</v>
@@ -8266,10 +8266,10 @@
         <v>No</v>
       </c>
       <c r="H149" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.5 out of 10</v>
       </c>
       <c r="I149">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J149">
         <v>30</v>
@@ -8319,10 +8319,10 @@
         <v>No</v>
       </c>
       <c r="H150" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.7 out of 10</v>
       </c>
       <c r="I150">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J150">
         <v>30</v>
@@ -8372,10 +8372,10 @@
         <v>No</v>
       </c>
       <c r="H151" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.3 out of 10</v>
       </c>
       <c r="I151">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J151">
         <v>30</v>
@@ -8425,10 +8425,10 @@
         <v>No</v>
       </c>
       <c r="H152" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I152">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="J152">
         <v>30</v>
@@ -8478,10 +8478,10 @@
         <v>No</v>
       </c>
       <c r="H153" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.2 out of 10</v>
       </c>
       <c r="I153">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="J153">
         <v>30</v>
@@ -8531,10 +8531,10 @@
         <v>No</v>
       </c>
       <c r="H154" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.3 out of 10</v>
       </c>
       <c r="I154">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J154">
         <v>30</v>
@@ -8584,10 +8584,10 @@
         <v>No</v>
       </c>
       <c r="H155" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.6 out of 10</v>
       </c>
       <c r="I155">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J155">
         <v>30</v>
@@ -8637,10 +8637,10 @@
         <v>No</v>
       </c>
       <c r="H156" t="str">
-        <v>6.5 out of 10</v>
+        <v>6 out of 10</v>
       </c>
       <c r="I156">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J156">
         <v>30</v>
@@ -8690,10 +8690,10 @@
         <v>No</v>
       </c>
       <c r="H157" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I157">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="J157">
         <v>30</v>
@@ -8743,10 +8743,10 @@
         <v>No</v>
       </c>
       <c r="H158" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I158">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="J158">
         <v>30</v>
@@ -8796,10 +8796,10 @@
         <v>No</v>
       </c>
       <c r="H159" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I159">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="J159">
         <v>30</v>
@@ -8849,10 +8849,10 @@
         <v>No</v>
       </c>
       <c r="H160" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.2 out of 10</v>
       </c>
       <c r="I160">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J160">
         <v>30</v>
@@ -8902,10 +8902,10 @@
         <v>No</v>
       </c>
       <c r="H161" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.4 out of 10</v>
       </c>
       <c r="I161">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J161">
         <v>30</v>
@@ -8955,10 +8955,10 @@
         <v>No</v>
       </c>
       <c r="H162" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.9 out of 10</v>
       </c>
       <c r="I162">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J162">
         <v>30</v>
@@ -9008,10 +9008,10 @@
         <v>No</v>
       </c>
       <c r="H163" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.8 out of 10</v>
       </c>
       <c r="I163">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J163">
         <v>30</v>
@@ -9061,10 +9061,10 @@
         <v>No</v>
       </c>
       <c r="H164" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.4 out of 10</v>
       </c>
       <c r="I164">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J164">
         <v>30</v>
@@ -9114,10 +9114,10 @@
         <v>No</v>
       </c>
       <c r="H165" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.2 out of 10</v>
       </c>
       <c r="I165">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J165">
         <v>30</v>
@@ -9167,10 +9167,10 @@
         <v>No</v>
       </c>
       <c r="H166" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.3 out of 10</v>
       </c>
       <c r="I166">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J166">
         <v>30</v>
@@ -9220,10 +9220,10 @@
         <v>No</v>
       </c>
       <c r="H167" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I167">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="J167">
         <v>30</v>
@@ -9273,10 +9273,10 @@
         <v>No</v>
       </c>
       <c r="H168" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.8 out of 10</v>
       </c>
       <c r="I168">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J168">
         <v>30</v>
@@ -9326,10 +9326,10 @@
         <v>No</v>
       </c>
       <c r="H169" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I169">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="J169">
         <v>30</v>
@@ -9379,10 +9379,10 @@
         <v>No</v>
       </c>
       <c r="H170" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.2 out of 10</v>
       </c>
       <c r="I170">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J170">
         <v>30</v>
@@ -9432,10 +9432,10 @@
         <v>No</v>
       </c>
       <c r="H171" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I171">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="J171">
         <v>30</v>
@@ -9485,10 +9485,10 @@
         <v>No</v>
       </c>
       <c r="H172" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I172">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="J172">
         <v>30</v>
@@ -9538,10 +9538,10 @@
         <v>No</v>
       </c>
       <c r="H173" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.5 out of 10</v>
       </c>
       <c r="I173">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="J173">
         <v>30</v>
@@ -9591,10 +9591,10 @@
         <v>No</v>
       </c>
       <c r="H174" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.4 out of 10</v>
       </c>
       <c r="I174">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="J174">
         <v>30</v>
@@ -9644,10 +9644,10 @@
         <v>No</v>
       </c>
       <c r="H175" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.3 out of 10</v>
       </c>
       <c r="I175">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J175">
         <v>30</v>
@@ -9697,10 +9697,10 @@
         <v>No</v>
       </c>
       <c r="H176" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.2 out of 10</v>
       </c>
       <c r="I176">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J176">
         <v>30</v>
@@ -9750,10 +9750,10 @@
         <v>No</v>
       </c>
       <c r="H177" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.6 out of 10</v>
       </c>
       <c r="I177">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="J177">
         <v>30</v>
@@ -9803,10 +9803,10 @@
         <v>No</v>
       </c>
       <c r="H178" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I178">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="J178">
         <v>30</v>
@@ -9856,10 +9856,10 @@
         <v>No</v>
       </c>
       <c r="H179" t="str">
-        <v>6.5 out of 10</v>
+        <v>7 out of 10</v>
       </c>
       <c r="I179">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J179">
         <v>30</v>
@@ -9909,10 +9909,10 @@
         <v>No</v>
       </c>
       <c r="H180" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.1 out of 10</v>
       </c>
       <c r="I180">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="J180">
         <v>30</v>
@@ -9962,10 +9962,10 @@
         <v>No</v>
       </c>
       <c r="H181" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I181">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J181">
         <v>30</v>
@@ -10015,10 +10015,10 @@
         <v>No</v>
       </c>
       <c r="H182" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.3 out of 10</v>
       </c>
       <c r="I182">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J182">
         <v>30</v>
@@ -10068,10 +10068,10 @@
         <v>No</v>
       </c>
       <c r="H183" t="str">
-        <v>6.5 out of 10</v>
+        <v>3 out of 10</v>
       </c>
       <c r="I183">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="J183">
         <v>30</v>
@@ -10121,10 +10121,10 @@
         <v>No</v>
       </c>
       <c r="H184" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.1 out of 10</v>
       </c>
       <c r="I184">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J184">
         <v>30</v>
@@ -10174,10 +10174,10 @@
         <v>No</v>
       </c>
       <c r="H185" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.6 out of 10</v>
       </c>
       <c r="I185">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J185">
         <v>30</v>
@@ -10227,10 +10227,10 @@
         <v>No</v>
       </c>
       <c r="H186" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I186">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="J186">
         <v>30</v>
@@ -10280,10 +10280,10 @@
         <v>No</v>
       </c>
       <c r="H187" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.7 out of 10</v>
       </c>
       <c r="I187">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="J187">
         <v>30</v>
@@ -10333,10 +10333,10 @@
         <v>No</v>
       </c>
       <c r="H188" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.3 out of 10</v>
       </c>
       <c r="I188">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J188">
         <v>30</v>
@@ -10386,10 +10386,10 @@
         <v>No</v>
       </c>
       <c r="H189" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.1 out of 10</v>
       </c>
       <c r="I189">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J189">
         <v>30</v>
@@ -10439,10 +10439,10 @@
         <v>No</v>
       </c>
       <c r="H190" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I190">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="J190">
         <v>30</v>
@@ -10492,10 +10492,10 @@
         <v>No</v>
       </c>
       <c r="H191" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I191">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="J191">
         <v>30</v>
@@ -10545,10 +10545,10 @@
         <v>No</v>
       </c>
       <c r="H192" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.4 out of 10</v>
       </c>
       <c r="I192">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J192">
         <v>30</v>
@@ -10598,10 +10598,10 @@
         <v>No</v>
       </c>
       <c r="H193" t="str">
-        <v>6.5 out of 10</v>
+        <v>3 out of 10</v>
       </c>
       <c r="I193">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="J193">
         <v>30</v>
@@ -10651,10 +10651,10 @@
         <v>No</v>
       </c>
       <c r="H194" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I194">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="J194">
         <v>30</v>
@@ -10704,10 +10704,10 @@
         <v>No</v>
       </c>
       <c r="H195" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.8 out of 10</v>
       </c>
       <c r="I195">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J195">
         <v>30</v>
@@ -10757,10 +10757,10 @@
         <v>No</v>
       </c>
       <c r="H196" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.3 out of 10</v>
       </c>
       <c r="I196">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J196">
         <v>30</v>
@@ -10810,10 +10810,10 @@
         <v>No</v>
       </c>
       <c r="H197" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.5 out of 10</v>
       </c>
       <c r="I197">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J197">
         <v>30</v>
@@ -10863,10 +10863,10 @@
         <v>No</v>
       </c>
       <c r="H198" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I198">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="J198">
         <v>30</v>
@@ -10916,10 +10916,10 @@
         <v>No</v>
       </c>
       <c r="H199" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I199">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="J199">
         <v>30</v>
@@ -10969,10 +10969,10 @@
         <v>No</v>
       </c>
       <c r="H200" t="str">
-        <v>6.5 out of 10</v>
+        <v>2 out of 10</v>
       </c>
       <c r="I200">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="J200">
         <v>30</v>
@@ -11022,10 +11022,10 @@
         <v>No</v>
       </c>
       <c r="H201" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.3 out of 10</v>
       </c>
       <c r="I201">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J201">
         <v>30</v>
@@ -11075,10 +11075,10 @@
         <v>No</v>
       </c>
       <c r="H202" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.3 out of 10</v>
       </c>
       <c r="I202">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J202">
         <v>30</v>
@@ -11128,10 +11128,10 @@
         <v>No</v>
       </c>
       <c r="H203" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.6 out of 10</v>
       </c>
       <c r="I203">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J203">
         <v>30</v>
@@ -11181,10 +11181,10 @@
         <v>No</v>
       </c>
       <c r="H204" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.3 out of 10</v>
       </c>
       <c r="I204">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J204">
         <v>30</v>
@@ -11234,10 +11234,10 @@
         <v>No</v>
       </c>
       <c r="H205" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I205">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="J205">
         <v>30</v>
@@ -11287,10 +11287,10 @@
         <v>No</v>
       </c>
       <c r="H206" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.8 out of 10</v>
       </c>
       <c r="I206">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J206">
         <v>30</v>
@@ -11340,10 +11340,10 @@
         <v>No</v>
       </c>
       <c r="H207" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I207">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="J207">
         <v>30</v>
@@ -11393,10 +11393,10 @@
         <v>No</v>
       </c>
       <c r="H208" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I208">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="J208">
         <v>30</v>
@@ -11446,10 +11446,10 @@
         <v>No</v>
       </c>
       <c r="H209" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.4 out of 10</v>
       </c>
       <c r="I209">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="J209">
         <v>30</v>
@@ -11499,10 +11499,10 @@
         <v>No</v>
       </c>
       <c r="H210" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I210">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="J210">
         <v>30</v>
@@ -11552,10 +11552,10 @@
         <v>No</v>
       </c>
       <c r="H211" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I211">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="J211">
         <v>30</v>
@@ -11605,10 +11605,10 @@
         <v>No</v>
       </c>
       <c r="H212" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I212">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="J212">
         <v>30</v>
@@ -11658,10 +11658,10 @@
         <v>No</v>
       </c>
       <c r="H213" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.6 out of 10</v>
       </c>
       <c r="I213">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J213">
         <v>30</v>
@@ -11711,10 +11711,10 @@
         <v>No</v>
       </c>
       <c r="H214" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.4 out of 10</v>
       </c>
       <c r="I214">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J214">
         <v>30</v>
@@ -11764,10 +11764,10 @@
         <v>No</v>
       </c>
       <c r="H215" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I215">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="J215">
         <v>30</v>
@@ -11817,10 +11817,10 @@
         <v>No</v>
       </c>
       <c r="H216" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.6 out of 10</v>
       </c>
       <c r="I216">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J216">
         <v>30</v>
@@ -11870,10 +11870,10 @@
         <v>No</v>
       </c>
       <c r="H217" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.1 out of 10</v>
       </c>
       <c r="I217">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J217">
         <v>30</v>
@@ -11923,10 +11923,10 @@
         <v>No</v>
       </c>
       <c r="H218" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.7 out of 10</v>
       </c>
       <c r="I218">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J218">
         <v>30</v>
@@ -11976,10 +11976,10 @@
         <v>No</v>
       </c>
       <c r="H219" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.6 out of 10</v>
       </c>
       <c r="I219">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J219">
         <v>30</v>
@@ -12029,10 +12029,10 @@
         <v>No</v>
       </c>
       <c r="H220" t="str">
-        <v>6.5 out of 10</v>
+        <v>7 out of 10</v>
       </c>
       <c r="I220">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J220">
         <v>30</v>
@@ -12082,10 +12082,10 @@
         <v>No</v>
       </c>
       <c r="H221" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.1 out of 10</v>
       </c>
       <c r="I221">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J221">
         <v>30</v>
@@ -12135,10 +12135,10 @@
         <v>No</v>
       </c>
       <c r="H222" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.2 out of 10</v>
       </c>
       <c r="I222">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="J222">
         <v>30</v>
@@ -12188,10 +12188,10 @@
         <v>No</v>
       </c>
       <c r="H223" t="str">
-        <v>6.5 out of 10</v>
+        <v>6 out of 10</v>
       </c>
       <c r="I223">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J223">
         <v>30</v>
@@ -12241,10 +12241,10 @@
         <v>No</v>
       </c>
       <c r="H224" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I224">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="J224">
         <v>30</v>
@@ -12294,10 +12294,10 @@
         <v>No</v>
       </c>
       <c r="H225" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.4 out of 10</v>
       </c>
       <c r="I225">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J225">
         <v>30</v>
@@ -12347,10 +12347,10 @@
         <v>No</v>
       </c>
       <c r="H226" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.9 out of 10</v>
       </c>
       <c r="I226">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J226">
         <v>30</v>
@@ -12400,10 +12400,10 @@
         <v>No</v>
       </c>
       <c r="H227" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I227">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J227">
         <v>30</v>
@@ -12453,10 +12453,10 @@
         <v>No</v>
       </c>
       <c r="H228" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.8 out of 10</v>
       </c>
       <c r="I228">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J228">
         <v>30</v>
@@ -12506,10 +12506,10 @@
         <v>No</v>
       </c>
       <c r="H229" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.2 out of 10</v>
       </c>
       <c r="I229">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J229">
         <v>30</v>
@@ -12559,10 +12559,10 @@
         <v>No</v>
       </c>
       <c r="H230" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.7 out of 10</v>
       </c>
       <c r="I230">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J230">
         <v>30</v>
@@ -12612,10 +12612,10 @@
         <v>No</v>
       </c>
       <c r="H231" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I231">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="J231">
         <v>30</v>
@@ -12665,10 +12665,10 @@
         <v>No</v>
       </c>
       <c r="H232" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.6 out of 10</v>
       </c>
       <c r="I232">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J232">
         <v>30</v>
@@ -12718,10 +12718,10 @@
         <v>No</v>
       </c>
       <c r="H233" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.4 out of 10</v>
       </c>
       <c r="I233">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="J233">
         <v>30</v>
@@ -12771,10 +12771,10 @@
         <v>No</v>
       </c>
       <c r="H234" t="str">
-        <v>6.5 out of 10</v>
+        <v>2 out of 10</v>
       </c>
       <c r="I234">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="J234">
         <v>30</v>
@@ -12824,10 +12824,10 @@
         <v>No</v>
       </c>
       <c r="H235" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I235">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="J235">
         <v>30</v>
@@ -12877,10 +12877,10 @@
         <v>No</v>
       </c>
       <c r="H236" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I236">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="J236">
         <v>30</v>
@@ -12930,10 +12930,10 @@
         <v>No</v>
       </c>
       <c r="H237" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I237">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="J237">
         <v>30</v>
@@ -12983,10 +12983,10 @@
         <v>No</v>
       </c>
       <c r="H238" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I238">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="J238">
         <v>30</v>
@@ -13036,10 +13036,10 @@
         <v>No</v>
       </c>
       <c r="H239" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.4 out of 10</v>
       </c>
       <c r="I239">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="J239">
         <v>30</v>
@@ -13089,10 +13089,10 @@
         <v>No</v>
       </c>
       <c r="H240" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.7 out of 10</v>
       </c>
       <c r="I240">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J240">
         <v>30</v>
@@ -13142,10 +13142,10 @@
         <v>No</v>
       </c>
       <c r="H241" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.6 out of 10</v>
       </c>
       <c r="I241">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="J241">
         <v>30</v>
@@ -13195,10 +13195,10 @@
         <v>No</v>
       </c>
       <c r="H242" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.4 out of 10</v>
       </c>
       <c r="I242">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J242">
         <v>30</v>
@@ -13248,10 +13248,10 @@
         <v>No</v>
       </c>
       <c r="H243" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I243">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="J243">
         <v>30</v>
@@ -13301,10 +13301,10 @@
         <v>No</v>
       </c>
       <c r="H244" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I244">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J244">
         <v>30</v>
@@ -13354,10 +13354,10 @@
         <v>No</v>
       </c>
       <c r="H245" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.4 out of 10</v>
       </c>
       <c r="I245">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="J245">
         <v>30</v>
@@ -13407,10 +13407,10 @@
         <v>No</v>
       </c>
       <c r="H246" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.4 out of 10</v>
       </c>
       <c r="I246">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J246">
         <v>30</v>
@@ -13460,10 +13460,10 @@
         <v>No</v>
       </c>
       <c r="H247" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I247">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="J247">
         <v>30</v>
@@ -13513,10 +13513,10 @@
         <v>No</v>
       </c>
       <c r="H248" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I248">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="J248">
         <v>30</v>
@@ -13566,10 +13566,10 @@
         <v>No</v>
       </c>
       <c r="H249" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.8 out of 10</v>
       </c>
       <c r="I249">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J249">
         <v>30</v>
@@ -13619,10 +13619,10 @@
         <v>No</v>
       </c>
       <c r="H250" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.7 out of 10</v>
       </c>
       <c r="I250">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="J250">
         <v>30</v>
@@ -13672,10 +13672,10 @@
         <v>No</v>
       </c>
       <c r="H251" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.8 out of 10</v>
       </c>
       <c r="I251">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J251">
         <v>30</v>
@@ -13725,10 +13725,10 @@
         <v>No</v>
       </c>
       <c r="H252" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.4 out of 10</v>
       </c>
       <c r="I252">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J252">
         <v>30</v>
@@ -13778,10 +13778,10 @@
         <v>No</v>
       </c>
       <c r="H253" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I253">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="J253">
         <v>30</v>
@@ -13831,10 +13831,10 @@
         <v>No</v>
       </c>
       <c r="H254" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.3 out of 10</v>
       </c>
       <c r="I254">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J254">
         <v>30</v>
@@ -13884,10 +13884,10 @@
         <v>No</v>
       </c>
       <c r="H255" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I255">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="J255">
         <v>30</v>
@@ -13937,10 +13937,10 @@
         <v>No</v>
       </c>
       <c r="H256" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.1 out of 10</v>
       </c>
       <c r="I256">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J256">
         <v>30</v>
@@ -13990,10 +13990,10 @@
         <v>No</v>
       </c>
       <c r="H257" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I257">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="J257">
         <v>30</v>
@@ -14043,10 +14043,10 @@
         <v>No</v>
       </c>
       <c r="H258" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I258">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="J258">
         <v>30</v>
@@ -14096,10 +14096,10 @@
         <v>No</v>
       </c>
       <c r="H259" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I259">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J259">
         <v>30</v>
@@ -14149,10 +14149,10 @@
         <v>No</v>
       </c>
       <c r="H260" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.4 out of 10</v>
       </c>
       <c r="I260">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J260">
         <v>30</v>
@@ -14202,10 +14202,10 @@
         <v>No</v>
       </c>
       <c r="H261" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.4 out of 10</v>
       </c>
       <c r="I261">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J261">
         <v>30</v>
@@ -14255,10 +14255,10 @@
         <v>No</v>
       </c>
       <c r="H262" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I262">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="J262">
         <v>30</v>
@@ -14308,10 +14308,10 @@
         <v>No</v>
       </c>
       <c r="H263" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.6 out of 10</v>
       </c>
       <c r="I263">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J263">
         <v>30</v>
@@ -14361,10 +14361,10 @@
         <v>No</v>
       </c>
       <c r="H264" t="str">
-        <v>6.5 out of 10</v>
+        <v>2 out of 10</v>
       </c>
       <c r="I264">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="J264">
         <v>30</v>
@@ -14414,10 +14414,10 @@
         <v>No</v>
       </c>
       <c r="H265" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.6 out of 10</v>
       </c>
       <c r="I265">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J265">
         <v>30</v>
@@ -14467,10 +14467,10 @@
         <v>No</v>
       </c>
       <c r="H266" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.5 out of 10</v>
       </c>
       <c r="I266">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J266">
         <v>30</v>
@@ -14520,10 +14520,10 @@
         <v>No</v>
       </c>
       <c r="H267" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.4 out of 10</v>
       </c>
       <c r="I267">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="J267">
         <v>30</v>
@@ -14573,10 +14573,10 @@
         <v>No</v>
       </c>
       <c r="H268" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.5 out of 10</v>
       </c>
       <c r="I268">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="J268">
         <v>30</v>
@@ -14626,10 +14626,10 @@
         <v>No</v>
       </c>
       <c r="H269" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.2 out of 10</v>
       </c>
       <c r="I269">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J269">
         <v>30</v>
@@ -14679,10 +14679,10 @@
         <v>No</v>
       </c>
       <c r="H270" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.6 out of 10</v>
       </c>
       <c r="I270">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J270">
         <v>30</v>
@@ -14732,10 +14732,10 @@
         <v>No</v>
       </c>
       <c r="H271" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.5 out of 10</v>
       </c>
       <c r="I271">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="J271">
         <v>30</v>
@@ -14785,10 +14785,10 @@
         <v>No</v>
       </c>
       <c r="H272" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I272">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="J272">
         <v>30</v>
@@ -14838,10 +14838,10 @@
         <v>No</v>
       </c>
       <c r="H273" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I273">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="J273">
         <v>30</v>
@@ -14891,10 +14891,10 @@
         <v>No</v>
       </c>
       <c r="H274" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.2 out of 10</v>
       </c>
       <c r="I274">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="J274">
         <v>30</v>
@@ -14944,10 +14944,10 @@
         <v>No</v>
       </c>
       <c r="H275" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.4 out of 10</v>
       </c>
       <c r="I275">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="J275">
         <v>30</v>
@@ -14997,10 +14997,10 @@
         <v>No</v>
       </c>
       <c r="H276" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I276">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="J276">
         <v>30</v>
@@ -15050,10 +15050,10 @@
         <v>No</v>
       </c>
       <c r="H277" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.8 out of 10</v>
       </c>
       <c r="I277">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J277">
         <v>30</v>
@@ -15103,10 +15103,10 @@
         <v>No</v>
       </c>
       <c r="H278" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I278">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J278">
         <v>30</v>
@@ -15156,10 +15156,10 @@
         <v>No</v>
       </c>
       <c r="H279" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.2 out of 10</v>
       </c>
       <c r="I279">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J279">
         <v>30</v>
@@ -15209,10 +15209,10 @@
         <v>No</v>
       </c>
       <c r="H280" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.2 out of 10</v>
       </c>
       <c r="I280">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J280">
         <v>30</v>
@@ -15262,10 +15262,10 @@
         <v>No</v>
       </c>
       <c r="H281" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.8 out of 10</v>
       </c>
       <c r="I281">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="J281">
         <v>30</v>
@@ -15315,10 +15315,10 @@
         <v>No</v>
       </c>
       <c r="H282" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I282">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="J282">
         <v>30</v>
@@ -15368,10 +15368,10 @@
         <v>No</v>
       </c>
       <c r="H283" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I283">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="J283">
         <v>30</v>
@@ -15421,10 +15421,10 @@
         <v>No</v>
       </c>
       <c r="H284" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.8 out of 10</v>
       </c>
       <c r="I284">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J284">
         <v>30</v>
@@ -15474,10 +15474,10 @@
         <v>No</v>
       </c>
       <c r="H285" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.4 out of 10</v>
       </c>
       <c r="I285">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="J285">
         <v>30</v>
@@ -15527,10 +15527,10 @@
         <v>No</v>
       </c>
       <c r="H286" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.6 out of 10</v>
       </c>
       <c r="I286">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J286">
         <v>30</v>
@@ -15580,10 +15580,10 @@
         <v>No</v>
       </c>
       <c r="H287" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.2 out of 10</v>
       </c>
       <c r="I287">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="J287">
         <v>30</v>
@@ -15633,10 +15633,10 @@
         <v>No</v>
       </c>
       <c r="H288" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.9 out of 10</v>
       </c>
       <c r="I288">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J288">
         <v>30</v>
@@ -15686,10 +15686,10 @@
         <v>No</v>
       </c>
       <c r="H289" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.2 out of 10</v>
       </c>
       <c r="I289">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J289">
         <v>30</v>
@@ -15739,10 +15739,10 @@
         <v>No</v>
       </c>
       <c r="H290" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I290">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="J290">
         <v>30</v>
@@ -15792,10 +15792,10 @@
         <v>No</v>
       </c>
       <c r="H291" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I291">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="J291">
         <v>30</v>
@@ -15845,10 +15845,10 @@
         <v>No</v>
       </c>
       <c r="H292" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.8 out of 10</v>
       </c>
       <c r="I292">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="J292">
         <v>30</v>
@@ -15898,10 +15898,10 @@
         <v>No</v>
       </c>
       <c r="H293" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.7 out of 10</v>
       </c>
       <c r="I293">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J293">
         <v>30</v>
@@ -15951,10 +15951,10 @@
         <v>No</v>
       </c>
       <c r="H294" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.8 out of 10</v>
       </c>
       <c r="I294">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="J294">
         <v>30</v>
@@ -16004,10 +16004,10 @@
         <v>No</v>
       </c>
       <c r="H295" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.8 out of 10</v>
       </c>
       <c r="I295">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J295">
         <v>30</v>
@@ -16057,10 +16057,10 @@
         <v>No</v>
       </c>
       <c r="H296" t="str">
-        <v>6.5 out of 10</v>
+        <v>2 out of 10</v>
       </c>
       <c r="I296">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="J296">
         <v>30</v>
@@ -16110,10 +16110,10 @@
         <v>No</v>
       </c>
       <c r="H297" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I297">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="J297">
         <v>30</v>
@@ -16163,10 +16163,10 @@
         <v>No</v>
       </c>
       <c r="H298" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.6 out of 10</v>
       </c>
       <c r="I298">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J298">
         <v>30</v>
@@ -16216,10 +16216,10 @@
         <v>No</v>
       </c>
       <c r="H299" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.4 out of 10</v>
       </c>
       <c r="I299">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="J299">
         <v>30</v>
@@ -16269,10 +16269,10 @@
         <v>No</v>
       </c>
       <c r="H300" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.6 out of 10</v>
       </c>
       <c r="I300">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J300">
         <v>30</v>
@@ -16322,10 +16322,10 @@
         <v>No</v>
       </c>
       <c r="H301" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.4 out of 10</v>
       </c>
       <c r="I301">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="J301">
         <v>30</v>
@@ -16375,10 +16375,10 @@
         <v>No</v>
       </c>
       <c r="H302" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.7 out of 10</v>
       </c>
       <c r="I302">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="J302">
         <v>30</v>
@@ -16428,10 +16428,10 @@
         <v>No</v>
       </c>
       <c r="H303" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.2 out of 10</v>
       </c>
       <c r="I303">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J303">
         <v>30</v>
@@ -16481,10 +16481,10 @@
         <v>No</v>
       </c>
       <c r="H304" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.7 out of 10</v>
       </c>
       <c r="I304">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="J304">
         <v>30</v>
@@ -16534,10 +16534,10 @@
         <v>No</v>
       </c>
       <c r="H305" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.2 out of 10</v>
       </c>
       <c r="I305">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J305">
         <v>30</v>
@@ -16587,10 +16587,10 @@
         <v>No</v>
       </c>
       <c r="H306" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.2 out of 10</v>
       </c>
       <c r="I306">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J306">
         <v>30</v>
@@ -16640,10 +16640,10 @@
         <v>No</v>
       </c>
       <c r="H307" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I307">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="J307">
         <v>30</v>
@@ -16693,10 +16693,10 @@
         <v>No</v>
       </c>
       <c r="H308" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.5 out of 10</v>
       </c>
       <c r="I308">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J308">
         <v>30</v>
@@ -16746,10 +16746,10 @@
         <v>No</v>
       </c>
       <c r="H309" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.7 out of 10</v>
       </c>
       <c r="I309">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J309">
         <v>30</v>
@@ -16799,10 +16799,10 @@
         <v>No</v>
       </c>
       <c r="H310" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.2 out of 10</v>
       </c>
       <c r="I310">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="J310">
         <v>30</v>
@@ -16852,10 +16852,10 @@
         <v>No</v>
       </c>
       <c r="H311" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.1 out of 10</v>
       </c>
       <c r="I311">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J311">
         <v>30</v>
@@ -16905,10 +16905,10 @@
         <v>No</v>
       </c>
       <c r="H312" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.9 out of 10</v>
       </c>
       <c r="I312">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J312">
         <v>30</v>
@@ -16958,10 +16958,10 @@
         <v>No</v>
       </c>
       <c r="H313" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.9 out of 10</v>
       </c>
       <c r="I313">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J313">
         <v>30</v>
@@ -17011,10 +17011,10 @@
         <v>No</v>
       </c>
       <c r="H314" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.5 out of 10</v>
       </c>
       <c r="I314">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J314">
         <v>30</v>
@@ -17064,10 +17064,10 @@
         <v>No</v>
       </c>
       <c r="H315" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.2 out of 10</v>
       </c>
       <c r="I315">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J315">
         <v>30</v>
@@ -17117,10 +17117,10 @@
         <v>No</v>
       </c>
       <c r="H316" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I316">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="J316">
         <v>30</v>
@@ -17170,10 +17170,10 @@
         <v>No</v>
       </c>
       <c r="H317" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.3 out of 10</v>
       </c>
       <c r="I317">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J317">
         <v>30</v>
@@ -17223,10 +17223,10 @@
         <v>No</v>
       </c>
       <c r="H318" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I318">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="J318">
         <v>30</v>
@@ -17276,10 +17276,10 @@
         <v>No</v>
       </c>
       <c r="H319" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.1 out of 10</v>
       </c>
       <c r="I319">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J319">
         <v>30</v>
@@ -17329,10 +17329,10 @@
         <v>No</v>
       </c>
       <c r="H320" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I320">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="J320">
         <v>30</v>
@@ -17435,10 +17435,10 @@
         <v>No</v>
       </c>
       <c r="H322" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.3 out of 10</v>
       </c>
       <c r="I322">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J322">
         <v>30</v>
@@ -17488,10 +17488,10 @@
         <v>No</v>
       </c>
       <c r="H323" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.5 out of 10</v>
       </c>
       <c r="I323">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="J323">
         <v>30</v>
@@ -17541,10 +17541,10 @@
         <v>No</v>
       </c>
       <c r="H324" t="str">
-        <v>6.5 out of 10</v>
+        <v>2 out of 10</v>
       </c>
       <c r="I324">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="J324">
         <v>30</v>
@@ -17594,10 +17594,10 @@
         <v>No</v>
       </c>
       <c r="H325" t="str">
-        <v>6.5 out of 10</v>
+        <v>5 out of 10</v>
       </c>
       <c r="I325">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J325">
         <v>30</v>
@@ -17647,10 +17647,10 @@
         <v>No</v>
       </c>
       <c r="H326" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.1 out of 10</v>
       </c>
       <c r="I326">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J326">
         <v>30</v>
@@ -17700,10 +17700,10 @@
         <v>No</v>
       </c>
       <c r="H327" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.4 out of 10</v>
       </c>
       <c r="I327">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J327">
         <v>30</v>
@@ -17753,10 +17753,10 @@
         <v>No</v>
       </c>
       <c r="H328" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.2 out of 10</v>
       </c>
       <c r="I328">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="J328">
         <v>30</v>
@@ -17806,10 +17806,10 @@
         <v>No</v>
       </c>
       <c r="H329" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I329">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="J329">
         <v>30</v>
@@ -17859,10 +17859,10 @@
         <v>No</v>
       </c>
       <c r="H330" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.3 out of 10</v>
       </c>
       <c r="I330">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J330">
         <v>30</v>
@@ -17912,10 +17912,10 @@
         <v>No</v>
       </c>
       <c r="H331" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I331">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="J331">
         <v>30</v>
@@ -17965,10 +17965,10 @@
         <v>No</v>
       </c>
       <c r="H332" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.6 out of 10</v>
       </c>
       <c r="I332">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J332">
         <v>30</v>
@@ -18018,10 +18018,10 @@
         <v>No</v>
       </c>
       <c r="H333" t="str">
-        <v>6.5 out of 10</v>
+        <v>2 out of 10</v>
       </c>
       <c r="I333">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="J333">
         <v>30</v>
@@ -18071,10 +18071,10 @@
         <v>No</v>
       </c>
       <c r="H334" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.4 out of 10</v>
       </c>
       <c r="I334">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="J334">
         <v>30</v>
@@ -18124,10 +18124,10 @@
         <v>No</v>
       </c>
       <c r="H335" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.3 out of 10</v>
       </c>
       <c r="I335">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="J335">
         <v>30</v>
@@ -18177,10 +18177,10 @@
         <v>No</v>
       </c>
       <c r="H336" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.2 out of 10</v>
       </c>
       <c r="I336">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="J336">
         <v>30</v>
@@ -18230,10 +18230,10 @@
         <v>No</v>
       </c>
       <c r="H337" t="str">
-        <v>6.5 out of 10</v>
+        <v>7 out of 10</v>
       </c>
       <c r="I337">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J337">
         <v>30</v>
@@ -18283,10 +18283,10 @@
         <v>No</v>
       </c>
       <c r="H338" t="str">
-        <v>6.5 out of 10</v>
+        <v>5 out of 10</v>
       </c>
       <c r="I338">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J338">
         <v>30</v>
@@ -18336,10 +18336,10 @@
         <v>No</v>
       </c>
       <c r="H339" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.2 out of 10</v>
       </c>
       <c r="I339">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J339">
         <v>30</v>
@@ -18389,10 +18389,10 @@
         <v>No</v>
       </c>
       <c r="H340" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I340">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="J340">
         <v>30</v>
@@ -18442,10 +18442,10 @@
         <v>No</v>
       </c>
       <c r="H341" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.4 out of 10</v>
       </c>
       <c r="I341">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="J341">
         <v>30</v>
@@ -18495,10 +18495,10 @@
         <v>No</v>
       </c>
       <c r="H342" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I342">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="J342">
         <v>30</v>
@@ -18548,10 +18548,10 @@
         <v>No</v>
       </c>
       <c r="H343" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.7 out of 10</v>
       </c>
       <c r="I343">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="J343">
         <v>30</v>
@@ -18601,10 +18601,10 @@
         <v>No</v>
       </c>
       <c r="H344" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I344">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="J344">
         <v>30</v>
@@ -18654,10 +18654,10 @@
         <v>No</v>
       </c>
       <c r="H345" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.5 out of 10</v>
       </c>
       <c r="I345">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="J345">
         <v>30</v>
@@ -18707,10 +18707,10 @@
         <v>No</v>
       </c>
       <c r="H346" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.3 out of 10</v>
       </c>
       <c r="I346">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="J346">
         <v>30</v>
@@ -18760,10 +18760,10 @@
         <v>No</v>
       </c>
       <c r="H347" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.4 out of 10</v>
       </c>
       <c r="I347">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J347">
         <v>30</v>
@@ -18813,10 +18813,10 @@
         <v>No</v>
       </c>
       <c r="H348" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I348">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="J348">
         <v>30</v>
@@ -18866,10 +18866,10 @@
         <v>No</v>
       </c>
       <c r="H349" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.4 out of 10</v>
       </c>
       <c r="I349">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J349">
         <v>30</v>
@@ -18919,10 +18919,10 @@
         <v>No</v>
       </c>
       <c r="H350" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I350">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="J350">
         <v>30</v>
@@ -18972,10 +18972,10 @@
         <v>No</v>
       </c>
       <c r="H351" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.8 out of 10</v>
       </c>
       <c r="I351">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J351">
         <v>30</v>
@@ -19025,10 +19025,10 @@
         <v>No</v>
       </c>
       <c r="H352" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.1 out of 10</v>
       </c>
       <c r="I352">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J352">
         <v>30</v>
@@ -19078,10 +19078,10 @@
         <v>No</v>
       </c>
       <c r="H353" t="str">
-        <v>6.5 out of 10</v>
+        <v>3 out of 10</v>
       </c>
       <c r="I353">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="J353">
         <v>30</v>
@@ -19131,10 +19131,10 @@
         <v>No</v>
       </c>
       <c r="H354" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I354">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="J354">
         <v>30</v>
@@ -19184,10 +19184,10 @@
         <v>No</v>
       </c>
       <c r="H355" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.3 out of 10</v>
       </c>
       <c r="I355">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J355">
         <v>30</v>
@@ -19237,10 +19237,10 @@
         <v>No</v>
       </c>
       <c r="H356" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I356">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="J356">
         <v>30</v>
@@ -19290,10 +19290,10 @@
         <v>No</v>
       </c>
       <c r="H357" t="str">
-        <v>6.5 out of 10</v>
+        <v>2 out of 10</v>
       </c>
       <c r="I357">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="J357">
         <v>30</v>
@@ -19343,10 +19343,10 @@
         <v>No</v>
       </c>
       <c r="H358" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.5 out of 10</v>
       </c>
       <c r="I358">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="J358">
         <v>30</v>
@@ -19396,10 +19396,10 @@
         <v>No</v>
       </c>
       <c r="H359" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.4 out of 10</v>
       </c>
       <c r="I359">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J359">
         <v>30</v>
@@ -19449,10 +19449,10 @@
         <v>No</v>
       </c>
       <c r="H360" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.7 out of 10</v>
       </c>
       <c r="I360">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J360">
         <v>30</v>
@@ -19502,10 +19502,10 @@
         <v>No</v>
       </c>
       <c r="H361" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I361">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J361">
         <v>30</v>
@@ -19555,10 +19555,10 @@
         <v>No</v>
       </c>
       <c r="H362" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.3 out of 10</v>
       </c>
       <c r="I362">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J362">
         <v>30</v>
@@ -19608,10 +19608,10 @@
         <v>No</v>
       </c>
       <c r="H363" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.5 out of 10</v>
       </c>
       <c r="I363">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J363">
         <v>30</v>
@@ -19661,10 +19661,10 @@
         <v>No</v>
       </c>
       <c r="H364" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.8 out of 10</v>
       </c>
       <c r="I364">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J364">
         <v>30</v>
@@ -19714,10 +19714,10 @@
         <v>No</v>
       </c>
       <c r="H365" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.8 out of 10</v>
       </c>
       <c r="I365">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J365">
         <v>30</v>
@@ -19767,10 +19767,10 @@
         <v>No</v>
       </c>
       <c r="H366" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.1 out of 10</v>
       </c>
       <c r="I366">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J366">
         <v>30</v>
@@ -19820,10 +19820,10 @@
         <v>No</v>
       </c>
       <c r="H367" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.3 out of 10</v>
       </c>
       <c r="I367">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J367">
         <v>30</v>
@@ -19926,10 +19926,10 @@
         <v>No</v>
       </c>
       <c r="H369" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.6 out of 10</v>
       </c>
       <c r="I369">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J369">
         <v>30</v>
@@ -19979,10 +19979,10 @@
         <v>No</v>
       </c>
       <c r="H370" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I370">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="J370">
         <v>30</v>
@@ -20032,10 +20032,10 @@
         <v>No</v>
       </c>
       <c r="H371" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.8 out of 10</v>
       </c>
       <c r="I371">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="J371">
         <v>30</v>
@@ -20085,10 +20085,10 @@
         <v>No</v>
       </c>
       <c r="H372" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.8 out of 10</v>
       </c>
       <c r="I372">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="J372">
         <v>30</v>
@@ -20138,10 +20138,10 @@
         <v>No</v>
       </c>
       <c r="H373" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.3 out of 10</v>
       </c>
       <c r="I373">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="J373">
         <v>30</v>
@@ -20191,10 +20191,10 @@
         <v>No</v>
       </c>
       <c r="H374" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.7 out of 10</v>
       </c>
       <c r="I374">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="J374">
         <v>30</v>
@@ -20244,10 +20244,10 @@
         <v>No</v>
       </c>
       <c r="H375" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.2 out of 10</v>
       </c>
       <c r="I375">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J375">
         <v>30</v>
@@ -20297,10 +20297,10 @@
         <v>No</v>
       </c>
       <c r="H376" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.7 out of 10</v>
       </c>
       <c r="I376">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J376">
         <v>30</v>
@@ -20350,10 +20350,10 @@
         <v>No</v>
       </c>
       <c r="H377" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.2 out of 10</v>
       </c>
       <c r="I377">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J377">
         <v>30</v>
@@ -20403,10 +20403,10 @@
         <v>No</v>
       </c>
       <c r="H378" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.2 out of 10</v>
       </c>
       <c r="I378">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J378">
         <v>30</v>
@@ -20456,10 +20456,10 @@
         <v>No</v>
       </c>
       <c r="H379" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.3 out of 10</v>
       </c>
       <c r="I379">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="J379">
         <v>30</v>
@@ -20509,10 +20509,10 @@
         <v>No</v>
       </c>
       <c r="H380" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I380">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="J380">
         <v>30</v>
@@ -20562,10 +20562,10 @@
         <v>No</v>
       </c>
       <c r="H381" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.4 out of 10</v>
       </c>
       <c r="I381">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J381">
         <v>30</v>
@@ -20615,10 +20615,10 @@
         <v>No</v>
       </c>
       <c r="H382" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.8 out of 10</v>
       </c>
       <c r="I382">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J382">
         <v>30</v>
@@ -20721,10 +20721,10 @@
         <v>No</v>
       </c>
       <c r="H384" t="str">
-        <v>6.5 out of 10</v>
+        <v>3 out of 10</v>
       </c>
       <c r="I384">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="J384">
         <v>30</v>
@@ -20774,10 +20774,10 @@
         <v>No</v>
       </c>
       <c r="H385" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I385">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="J385">
         <v>30</v>
@@ -20827,10 +20827,10 @@
         <v>No</v>
       </c>
       <c r="H386" t="str">
-        <v>6.5 out of 10</v>
+        <v>2 out of 10</v>
       </c>
       <c r="I386">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="J386">
         <v>30</v>
@@ -20880,10 +20880,10 @@
         <v>No</v>
       </c>
       <c r="H387" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I387">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="J387">
         <v>30</v>
@@ -20933,10 +20933,10 @@
         <v>No</v>
       </c>
       <c r="H388" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I388">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="J388">
         <v>30</v>
@@ -20986,10 +20986,10 @@
         <v>No</v>
       </c>
       <c r="H389" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.6 out of 10</v>
       </c>
       <c r="I389">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J389">
         <v>30</v>
@@ -21039,10 +21039,10 @@
         <v>No</v>
       </c>
       <c r="H390" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.7 out of 10</v>
       </c>
       <c r="I390">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J390">
         <v>30</v>
@@ -21092,10 +21092,10 @@
         <v>No</v>
       </c>
       <c r="H391" t="str">
-        <v>6.5 out of 10</v>
+        <v>6 out of 10</v>
       </c>
       <c r="I391">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J391">
         <v>30</v>
@@ -21145,10 +21145,10 @@
         <v>No</v>
       </c>
       <c r="H392" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.6 out of 10</v>
       </c>
       <c r="I392">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="J392">
         <v>30</v>
@@ -21198,10 +21198,10 @@
         <v>No</v>
       </c>
       <c r="H393" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.7 out of 10</v>
       </c>
       <c r="I393">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J393">
         <v>30</v>
@@ -21251,10 +21251,10 @@
         <v>No</v>
       </c>
       <c r="H394" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.4 out of 10</v>
       </c>
       <c r="I394">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J394">
         <v>30</v>
@@ -21304,10 +21304,10 @@
         <v>No</v>
       </c>
       <c r="H395" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.2 out of 10</v>
       </c>
       <c r="I395">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="J395">
         <v>30</v>
@@ -21357,10 +21357,10 @@
         <v>No</v>
       </c>
       <c r="H396" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I396">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="J396">
         <v>30</v>
@@ -21410,10 +21410,10 @@
         <v>No</v>
       </c>
       <c r="H397" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.3 out of 10</v>
       </c>
       <c r="I397">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J397">
         <v>30</v>
@@ -21463,10 +21463,10 @@
         <v>No</v>
       </c>
       <c r="H398" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.5 out of 10</v>
       </c>
       <c r="I398">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J398">
         <v>30</v>
@@ -21516,10 +21516,10 @@
         <v>No</v>
       </c>
       <c r="H399" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.6 out of 10</v>
       </c>
       <c r="I399">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="J399">
         <v>30</v>
@@ -21569,10 +21569,10 @@
         <v>No</v>
       </c>
       <c r="H400" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.4 out of 10</v>
       </c>
       <c r="I400">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J400">
         <v>30</v>
@@ -21622,10 +21622,10 @@
         <v>No</v>
       </c>
       <c r="H401" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.3 out of 10</v>
       </c>
       <c r="I401">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J401">
         <v>30</v>
@@ -21675,10 +21675,10 @@
         <v>No</v>
       </c>
       <c r="H402" t="str">
-        <v>6.5 out of 10</v>
+        <v>3 out of 10</v>
       </c>
       <c r="I402">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="J402">
         <v>30</v>
@@ -21728,10 +21728,10 @@
         <v>No</v>
       </c>
       <c r="H403" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I403">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="J403">
         <v>30</v>
@@ -21781,10 +21781,10 @@
         <v>No</v>
       </c>
       <c r="H404" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I404">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="J404">
         <v>30</v>
@@ -21834,10 +21834,10 @@
         <v>No</v>
       </c>
       <c r="H405" t="str">
-        <v>6.5 out of 10</v>
+        <v>2 out of 10</v>
       </c>
       <c r="I405">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="J405">
         <v>30</v>
@@ -21887,10 +21887,10 @@
         <v>No</v>
       </c>
       <c r="H406" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.2 out of 10</v>
       </c>
       <c r="I406">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J406">
         <v>30</v>
@@ -21940,10 +21940,10 @@
         <v>No</v>
       </c>
       <c r="H407" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.1 out of 10</v>
       </c>
       <c r="I407">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J407">
         <v>30</v>
@@ -21993,10 +21993,10 @@
         <v>No</v>
       </c>
       <c r="H408" t="str">
-        <v>6.5 out of 10</v>
+        <v>3 out of 10</v>
       </c>
       <c r="I408">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="J408">
         <v>30</v>
@@ -22046,10 +22046,10 @@
         <v>No</v>
       </c>
       <c r="H409" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.5 out of 10</v>
       </c>
       <c r="I409">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="J409">
         <v>30</v>
@@ -22099,10 +22099,10 @@
         <v>No</v>
       </c>
       <c r="H410" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.5 out of 10</v>
       </c>
       <c r="I410">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="J410">
         <v>30</v>
@@ -22152,10 +22152,10 @@
         <v>No</v>
       </c>
       <c r="H411" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.9 out of 10</v>
       </c>
       <c r="I411">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J411">
         <v>30</v>
@@ -22258,10 +22258,10 @@
         <v>No</v>
       </c>
       <c r="H413" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.4 out of 10</v>
       </c>
       <c r="I413">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J413">
         <v>30</v>
@@ -22311,10 +22311,10 @@
         <v>No</v>
       </c>
       <c r="H414" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.6 out of 10</v>
       </c>
       <c r="I414">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J414">
         <v>30</v>
@@ -22364,10 +22364,10 @@
         <v>No</v>
       </c>
       <c r="H415" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.6 out of 10</v>
       </c>
       <c r="I415">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J415">
         <v>30</v>
@@ -22417,10 +22417,10 @@
         <v>No</v>
       </c>
       <c r="H416" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.2 out of 10</v>
       </c>
       <c r="I416">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J416">
         <v>30</v>
@@ -22470,10 +22470,10 @@
         <v>No</v>
       </c>
       <c r="H417" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.8 out of 10</v>
       </c>
       <c r="I417">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="J417">
         <v>30</v>
@@ -22523,10 +22523,10 @@
         <v>No</v>
       </c>
       <c r="H418" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I418">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="J418">
         <v>30</v>
@@ -22576,10 +22576,10 @@
         <v>No</v>
       </c>
       <c r="H419" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.9 out of 10</v>
       </c>
       <c r="I419">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J419">
         <v>30</v>
@@ -22629,10 +22629,10 @@
         <v>No</v>
       </c>
       <c r="H420" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.3 out of 10</v>
       </c>
       <c r="I420">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J420">
         <v>30</v>
@@ -22682,10 +22682,10 @@
         <v>No</v>
       </c>
       <c r="H421" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I421">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J421">
         <v>30</v>
@@ -22735,10 +22735,10 @@
         <v>No</v>
       </c>
       <c r="H422" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.2 out of 10</v>
       </c>
       <c r="I422">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J422">
         <v>30</v>
@@ -22788,10 +22788,10 @@
         <v>No</v>
       </c>
       <c r="H423" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.8 out of 10</v>
       </c>
       <c r="I423">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="J423">
         <v>30</v>
@@ -22841,10 +22841,10 @@
         <v>No</v>
       </c>
       <c r="H424" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.3 out of 10</v>
       </c>
       <c r="I424">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J424">
         <v>30</v>
@@ -22894,10 +22894,10 @@
         <v>No</v>
       </c>
       <c r="H425" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.6 out of 10</v>
       </c>
       <c r="I425">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J425">
         <v>30</v>
@@ -22947,10 +22947,10 @@
         <v>No</v>
       </c>
       <c r="H426" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.9 out of 10</v>
       </c>
       <c r="I426">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J426">
         <v>30</v>
@@ -23000,10 +23000,10 @@
         <v>No</v>
       </c>
       <c r="H427" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.4 out of 10</v>
       </c>
       <c r="I427">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J427">
         <v>30</v>
@@ -23053,10 +23053,10 @@
         <v>No</v>
       </c>
       <c r="H428" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.6 out of 10</v>
       </c>
       <c r="I428">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J428">
         <v>30</v>
@@ -23106,10 +23106,10 @@
         <v>No</v>
       </c>
       <c r="H429" t="str">
-        <v>6.5 out of 10</v>
+        <v>3 out of 10</v>
       </c>
       <c r="I429">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="J429">
         <v>30</v>
@@ -23159,10 +23159,10 @@
         <v>No</v>
       </c>
       <c r="H430" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.5 out of 10</v>
       </c>
       <c r="I430">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J430">
         <v>30</v>
@@ -23212,10 +23212,10 @@
         <v>No</v>
       </c>
       <c r="H431" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.8 out of 10</v>
       </c>
       <c r="I431">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J431">
         <v>30</v>
@@ -23265,10 +23265,10 @@
         <v>No</v>
       </c>
       <c r="H432" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.2 out of 10</v>
       </c>
       <c r="I432">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J432">
         <v>30</v>
@@ -23318,10 +23318,10 @@
         <v>No</v>
       </c>
       <c r="H433" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.2 out of 10</v>
       </c>
       <c r="I433">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J433">
         <v>30</v>
@@ -23371,10 +23371,10 @@
         <v>No</v>
       </c>
       <c r="H434" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.4 out of 10</v>
       </c>
       <c r="I434">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="J434">
         <v>30</v>
@@ -23424,10 +23424,10 @@
         <v>No</v>
       </c>
       <c r="H435" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.2 out of 10</v>
       </c>
       <c r="I435">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="J435">
         <v>30</v>
@@ -23477,10 +23477,10 @@
         <v>No</v>
       </c>
       <c r="H436" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.6 out of 10</v>
       </c>
       <c r="I436">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J436">
         <v>30</v>
@@ -23530,10 +23530,10 @@
         <v>No</v>
       </c>
       <c r="H437" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.3 out of 10</v>
       </c>
       <c r="I437">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J437">
         <v>30</v>
@@ -23583,10 +23583,10 @@
         <v>No</v>
       </c>
       <c r="H438" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.3 out of 10</v>
       </c>
       <c r="I438">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J438">
         <v>30</v>
@@ -23636,10 +23636,10 @@
         <v>No</v>
       </c>
       <c r="H439" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I439">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="J439">
         <v>30</v>
@@ -23689,10 +23689,10 @@
         <v>No</v>
       </c>
       <c r="H440" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.1 out of 10</v>
       </c>
       <c r="I440">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="J440">
         <v>30</v>
@@ -23742,10 +23742,10 @@
         <v>No</v>
       </c>
       <c r="H441" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.9 out of 10</v>
       </c>
       <c r="I441">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J441">
         <v>30</v>
@@ -23795,10 +23795,10 @@
         <v>No</v>
       </c>
       <c r="H442" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.3 out of 10</v>
       </c>
       <c r="I442">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J442">
         <v>30</v>
@@ -23848,10 +23848,10 @@
         <v>No</v>
       </c>
       <c r="H443" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.8 out of 10</v>
       </c>
       <c r="I443">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="J443">
         <v>30</v>
@@ -23901,10 +23901,10 @@
         <v>No</v>
       </c>
       <c r="H444" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.6 out of 10</v>
       </c>
       <c r="I444">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J444">
         <v>30</v>
@@ -23954,10 +23954,10 @@
         <v>No</v>
       </c>
       <c r="H445" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.7 out of 10</v>
       </c>
       <c r="I445">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J445">
         <v>30</v>
@@ -24007,10 +24007,10 @@
         <v>No</v>
       </c>
       <c r="H446" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.3 out of 10</v>
       </c>
       <c r="I446">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J446">
         <v>30</v>
@@ -24060,10 +24060,10 @@
         <v>No</v>
       </c>
       <c r="H447" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.8 out of 10</v>
       </c>
       <c r="I447">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J447">
         <v>30</v>
@@ -24113,10 +24113,10 @@
         <v>No</v>
       </c>
       <c r="H448" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I448">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="J448">
         <v>30</v>
@@ -24166,10 +24166,10 @@
         <v>No</v>
       </c>
       <c r="H449" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.7 out of 10</v>
       </c>
       <c r="I449">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J449">
         <v>30</v>
@@ -24219,10 +24219,10 @@
         <v>No</v>
       </c>
       <c r="H450" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.2 out of 10</v>
       </c>
       <c r="I450">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J450">
         <v>30</v>
@@ -24272,10 +24272,10 @@
         <v>No</v>
       </c>
       <c r="H451" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.4 out of 10</v>
       </c>
       <c r="I451">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="J451">
         <v>30</v>
@@ -24325,10 +24325,10 @@
         <v>No</v>
       </c>
       <c r="H452" t="str">
-        <v>6.5 out of 10</v>
+        <v>6 out of 10</v>
       </c>
       <c r="I452">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J452">
         <v>30</v>
@@ -24378,10 +24378,10 @@
         <v>No</v>
       </c>
       <c r="H453" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.8 out of 10</v>
       </c>
       <c r="I453">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J453">
         <v>30</v>
@@ -24431,10 +24431,10 @@
         <v>No</v>
       </c>
       <c r="H454" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.8 out of 10</v>
       </c>
       <c r="I454">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J454">
         <v>30</v>
@@ -24484,10 +24484,10 @@
         <v>No</v>
       </c>
       <c r="H455" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I455">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="J455">
         <v>30</v>
@@ -24537,10 +24537,10 @@
         <v>No</v>
       </c>
       <c r="H456" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.3 out of 10</v>
       </c>
       <c r="I456">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J456">
         <v>30</v>
@@ -24590,10 +24590,10 @@
         <v>No</v>
       </c>
       <c r="H457" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.2 out of 10</v>
       </c>
       <c r="I457">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J457">
         <v>30</v>
@@ -24643,10 +24643,10 @@
         <v>No</v>
       </c>
       <c r="H458" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I458">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="J458">
         <v>30</v>
@@ -24696,10 +24696,10 @@
         <v>No</v>
       </c>
       <c r="H459" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.8 out of 10</v>
       </c>
       <c r="I459">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J459">
         <v>30</v>
@@ -24749,10 +24749,10 @@
         <v>No</v>
       </c>
       <c r="H460" t="str">
-        <v>6.5 out of 10</v>
+        <v>6 out of 10</v>
       </c>
       <c r="I460">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J460">
         <v>30</v>
@@ -24802,10 +24802,10 @@
         <v>No</v>
       </c>
       <c r="H461" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.8 out of 10</v>
       </c>
       <c r="I461">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J461">
         <v>30</v>
@@ -24855,10 +24855,10 @@
         <v>No</v>
       </c>
       <c r="H462" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.4 out of 10</v>
       </c>
       <c r="I462">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J462">
         <v>30</v>
@@ -24908,10 +24908,10 @@
         <v>No</v>
       </c>
       <c r="H463" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.4 out of 10</v>
       </c>
       <c r="I463">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J463">
         <v>30</v>
@@ -24961,10 +24961,10 @@
         <v>No</v>
       </c>
       <c r="H464" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.6 out of 10</v>
       </c>
       <c r="I464">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J464">
         <v>30</v>
@@ -25014,10 +25014,10 @@
         <v>No</v>
       </c>
       <c r="H465" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I465">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="J465">
         <v>30</v>
@@ -25067,10 +25067,10 @@
         <v>No</v>
       </c>
       <c r="H466" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.4 out of 10</v>
       </c>
       <c r="I466">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J466">
         <v>30</v>
@@ -25120,10 +25120,10 @@
         <v>No</v>
       </c>
       <c r="H467" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.8 out of 10</v>
       </c>
       <c r="I467">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J467">
         <v>30</v>
@@ -25173,10 +25173,10 @@
         <v>No</v>
       </c>
       <c r="H468" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I468">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="J468">
         <v>30</v>
@@ -25226,10 +25226,10 @@
         <v>No</v>
       </c>
       <c r="H469" t="str">
-        <v>6.5 out of 10</v>
+        <v>7 out of 10</v>
       </c>
       <c r="I469">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J469">
         <v>30</v>
@@ -25279,10 +25279,10 @@
         <v>No</v>
       </c>
       <c r="H470" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.2 out of 10</v>
       </c>
       <c r="I470">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="J470">
         <v>30</v>
@@ -25332,10 +25332,10 @@
         <v>No</v>
       </c>
       <c r="H471" t="str">
-        <v>6.5 out of 10</v>
+        <v>3 out of 10</v>
       </c>
       <c r="I471">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="J471">
         <v>30</v>
@@ -25385,10 +25385,10 @@
         <v>No</v>
       </c>
       <c r="H472" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.6 out of 10</v>
       </c>
       <c r="I472">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J472">
         <v>30</v>
@@ -25438,10 +25438,10 @@
         <v>No</v>
       </c>
       <c r="H473" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I473">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="J473">
         <v>30</v>
@@ -25491,10 +25491,10 @@
         <v>No</v>
       </c>
       <c r="H474" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.1 out of 10</v>
       </c>
       <c r="I474">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="J474">
         <v>30</v>
@@ -25544,10 +25544,10 @@
         <v>No</v>
       </c>
       <c r="H475" t="str">
-        <v>6.5 out of 10</v>
+        <v>6 out of 10</v>
       </c>
       <c r="I475">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J475">
         <v>30</v>
@@ -25597,10 +25597,10 @@
         <v>No</v>
       </c>
       <c r="H476" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.2 out of 10</v>
       </c>
       <c r="I476">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="J476">
         <v>30</v>
@@ -25650,10 +25650,10 @@
         <v>No</v>
       </c>
       <c r="H477" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I477">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="J477">
         <v>30</v>
@@ -25703,10 +25703,10 @@
         <v>No</v>
       </c>
       <c r="H478" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I478">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="J478">
         <v>30</v>
@@ -25756,10 +25756,10 @@
         <v>No</v>
       </c>
       <c r="H479" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.3 out of 10</v>
       </c>
       <c r="I479">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="J479">
         <v>30</v>
@@ -25809,10 +25809,10 @@
         <v>No</v>
       </c>
       <c r="H480" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.2 out of 10</v>
       </c>
       <c r="I480">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J480">
         <v>30</v>
@@ -25862,10 +25862,10 @@
         <v>No</v>
       </c>
       <c r="H481" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I481">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="J481">
         <v>30</v>
@@ -25915,10 +25915,10 @@
         <v>No</v>
       </c>
       <c r="H482" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I482">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="J482">
         <v>30</v>
@@ -25968,10 +25968,10 @@
         <v>No</v>
       </c>
       <c r="H483" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.9 out of 10</v>
       </c>
       <c r="I483">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J483">
         <v>30</v>
@@ -26021,10 +26021,10 @@
         <v>No</v>
       </c>
       <c r="H484" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.9 out of 10</v>
       </c>
       <c r="I484">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J484">
         <v>30</v>
@@ -26074,10 +26074,10 @@
         <v>No</v>
       </c>
       <c r="H485" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.6 out of 10</v>
       </c>
       <c r="I485">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J485">
         <v>30</v>
@@ -26127,10 +26127,10 @@
         <v>No</v>
       </c>
       <c r="H486" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.6 out of 10</v>
       </c>
       <c r="I486">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J486">
         <v>30</v>
@@ -26180,10 +26180,10 @@
         <v>No</v>
       </c>
       <c r="H487" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.1 out of 10</v>
       </c>
       <c r="I487">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J487">
         <v>30</v>
@@ -26233,10 +26233,10 @@
         <v>No</v>
       </c>
       <c r="H488" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I488">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="J488">
         <v>30</v>
@@ -26286,10 +26286,10 @@
         <v>No</v>
       </c>
       <c r="H489" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.2 out of 10</v>
       </c>
       <c r="I489">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="J489">
         <v>30</v>
@@ -26339,10 +26339,10 @@
         <v>No</v>
       </c>
       <c r="H490" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I490">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="J490">
         <v>30</v>
@@ -26392,10 +26392,10 @@
         <v>No</v>
       </c>
       <c r="H491" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.6 out of 10</v>
       </c>
       <c r="I491">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J491">
         <v>30</v>
@@ -26445,10 +26445,10 @@
         <v>No</v>
       </c>
       <c r="H492" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.3 out of 10</v>
       </c>
       <c r="I492">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J492">
         <v>30</v>
@@ -26498,10 +26498,10 @@
         <v>No</v>
       </c>
       <c r="H493" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I493">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J493">
         <v>30</v>
@@ -26604,10 +26604,10 @@
         <v>No</v>
       </c>
       <c r="H495" t="str">
-        <v>6.5 out of 10</v>
+        <v>2 out of 10</v>
       </c>
       <c r="I495">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="J495">
         <v>30</v>
@@ -26657,10 +26657,10 @@
         <v>No</v>
       </c>
       <c r="H496" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.8 out of 10</v>
       </c>
       <c r="I496">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J496">
         <v>30</v>
@@ -26710,10 +26710,10 @@
         <v>No</v>
       </c>
       <c r="H497" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.3 out of 10</v>
       </c>
       <c r="I497">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="J497">
         <v>30</v>
@@ -26763,10 +26763,10 @@
         <v>No</v>
       </c>
       <c r="H498" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.4 out of 10</v>
       </c>
       <c r="I498">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J498">
         <v>30</v>
@@ -26816,10 +26816,10 @@
         <v>No</v>
       </c>
       <c r="H499" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.4 out of 10</v>
       </c>
       <c r="I499">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J499">
         <v>30</v>
@@ -26869,10 +26869,10 @@
         <v>No</v>
       </c>
       <c r="H500" t="str">
-        <v>6.5 out of 10</v>
+        <v>2 out of 10</v>
       </c>
       <c r="I500">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="J500">
         <v>30</v>
@@ -26922,10 +26922,10 @@
         <v>No</v>
       </c>
       <c r="H501" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I501">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="J501">
         <v>30</v>
@@ -26975,10 +26975,10 @@
         <v>No</v>
       </c>
       <c r="H502" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.4 out of 10</v>
       </c>
       <c r="I502">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="J502">
         <v>30</v>
@@ -27028,10 +27028,10 @@
         <v>No</v>
       </c>
       <c r="H503" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I503">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J503">
         <v>30</v>
@@ -27081,10 +27081,10 @@
         <v>No</v>
       </c>
       <c r="H504" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.8 out of 10</v>
       </c>
       <c r="I504">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="J504">
         <v>30</v>
@@ -27134,10 +27134,10 @@
         <v>No</v>
       </c>
       <c r="H505" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.1 out of 10</v>
       </c>
       <c r="I505">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J505">
         <v>30</v>
@@ -27240,10 +27240,10 @@
         <v>No</v>
       </c>
       <c r="H507" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.9 out of 10</v>
       </c>
       <c r="I507">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J507">
         <v>30</v>
@@ -27293,10 +27293,10 @@
         <v>No</v>
       </c>
       <c r="H508" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I508">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="J508">
         <v>30</v>
@@ -27346,10 +27346,10 @@
         <v>No</v>
       </c>
       <c r="H509" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.8 out of 10</v>
       </c>
       <c r="I509">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J509">
         <v>30</v>
@@ -27399,10 +27399,10 @@
         <v>No</v>
       </c>
       <c r="H510" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I510">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="J510">
         <v>30</v>
@@ -27452,10 +27452,10 @@
         <v>No</v>
       </c>
       <c r="H511" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.2 out of 10</v>
       </c>
       <c r="I511">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J511">
         <v>30</v>
@@ -27505,10 +27505,10 @@
         <v>No</v>
       </c>
       <c r="H512" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.8 out of 10</v>
       </c>
       <c r="I512">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J512">
         <v>30</v>
@@ -27558,10 +27558,10 @@
         <v>No</v>
       </c>
       <c r="H513" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.6 out of 10</v>
       </c>
       <c r="I513">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J513">
         <v>30</v>
@@ -27611,10 +27611,10 @@
         <v>No</v>
       </c>
       <c r="H514" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I514">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="J514">
         <v>30</v>
@@ -27664,10 +27664,10 @@
         <v>No</v>
       </c>
       <c r="H515" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.7 out of 10</v>
       </c>
       <c r="I515">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J515">
         <v>30</v>
@@ -27717,10 +27717,10 @@
         <v>No</v>
       </c>
       <c r="H516" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.1 out of 10</v>
       </c>
       <c r="I516">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="J516">
         <v>30</v>
@@ -27770,10 +27770,10 @@
         <v>No</v>
       </c>
       <c r="H517" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.1 out of 10</v>
       </c>
       <c r="I517">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="J517">
         <v>30</v>
@@ -27823,10 +27823,10 @@
         <v>No</v>
       </c>
       <c r="H518" t="str">
-        <v>6.5 out of 10</v>
+        <v>3 out of 10</v>
       </c>
       <c r="I518">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="J518">
         <v>30</v>
@@ -27876,10 +27876,10 @@
         <v>No</v>
       </c>
       <c r="H519" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I519">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="J519">
         <v>30</v>
@@ -27929,10 +27929,10 @@
         <v>No</v>
       </c>
       <c r="H520" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.3 out of 10</v>
       </c>
       <c r="I520">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J520">
         <v>30</v>
@@ -27982,10 +27982,10 @@
         <v>No</v>
       </c>
       <c r="H521" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I521">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="J521">
         <v>30</v>
@@ -28035,10 +28035,10 @@
         <v>No</v>
       </c>
       <c r="H522" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.8 out of 10</v>
       </c>
       <c r="I522">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="J522">
         <v>30</v>
@@ -28088,10 +28088,10 @@
         <v>No</v>
       </c>
       <c r="H523" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.7 out of 10</v>
       </c>
       <c r="I523">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="J523">
         <v>30</v>
@@ -28141,10 +28141,10 @@
         <v>No</v>
       </c>
       <c r="H524" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.5 out of 10</v>
       </c>
       <c r="I524">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="J524">
         <v>30</v>
@@ -28194,10 +28194,10 @@
         <v>No</v>
       </c>
       <c r="H525" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.3 out of 10</v>
       </c>
       <c r="I525">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="J525">
         <v>30</v>
@@ -28247,10 +28247,10 @@
         <v>No</v>
       </c>
       <c r="H526" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I526">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J526">
         <v>30</v>
@@ -28300,10 +28300,10 @@
         <v>No</v>
       </c>
       <c r="H527" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.3 out of 10</v>
       </c>
       <c r="I527">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J527">
         <v>30</v>
@@ -28353,10 +28353,10 @@
         <v>No</v>
       </c>
       <c r="H528" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.6 out of 10</v>
       </c>
       <c r="I528">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J528">
         <v>30</v>
@@ -28406,10 +28406,10 @@
         <v>No</v>
       </c>
       <c r="H529" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.9 out of 10</v>
       </c>
       <c r="I529">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J529">
         <v>30</v>
@@ -28459,10 +28459,10 @@
         <v>No</v>
       </c>
       <c r="H530" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.7 out of 10</v>
       </c>
       <c r="I530">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J530">
         <v>30</v>
@@ -28512,10 +28512,10 @@
         <v>No</v>
       </c>
       <c r="H531" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I531">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="J531">
         <v>30</v>
@@ -28565,10 +28565,10 @@
         <v>No</v>
       </c>
       <c r="H532" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.3 out of 10</v>
       </c>
       <c r="I532">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J532">
         <v>30</v>
@@ -28618,10 +28618,10 @@
         <v>No</v>
       </c>
       <c r="H533" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I533">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="J533">
         <v>30</v>
@@ -28671,10 +28671,10 @@
         <v>No</v>
       </c>
       <c r="H534" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.6 out of 10</v>
       </c>
       <c r="I534">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="J534">
         <v>30</v>
@@ -28724,10 +28724,10 @@
         <v>No</v>
       </c>
       <c r="H535" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.6 out of 10</v>
       </c>
       <c r="I535">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J535">
         <v>30</v>
@@ -28777,10 +28777,10 @@
         <v>No</v>
       </c>
       <c r="H536" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.4 out of 10</v>
       </c>
       <c r="I536">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J536">
         <v>30</v>
@@ -28830,10 +28830,10 @@
         <v>No</v>
       </c>
       <c r="H537" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.4 out of 10</v>
       </c>
       <c r="I537">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="J537">
         <v>30</v>
@@ -28883,10 +28883,10 @@
         <v>No</v>
       </c>
       <c r="H538" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.4 out of 10</v>
       </c>
       <c r="I538">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="J538">
         <v>30</v>
@@ -28936,10 +28936,10 @@
         <v>No</v>
       </c>
       <c r="H539" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.6 out of 10</v>
       </c>
       <c r="I539">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J539">
         <v>30</v>
@@ -28989,10 +28989,10 @@
         <v>No</v>
       </c>
       <c r="H540" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.5 out of 10</v>
       </c>
       <c r="I540">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="J540">
         <v>30</v>
@@ -29042,10 +29042,10 @@
         <v>No</v>
       </c>
       <c r="H541" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I541">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="J541">
         <v>30</v>
@@ -29095,10 +29095,10 @@
         <v>No</v>
       </c>
       <c r="H542" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I542">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="J542">
         <v>30</v>
@@ -29148,10 +29148,10 @@
         <v>No</v>
       </c>
       <c r="H543" t="str">
-        <v>6.5 out of 10</v>
+        <v>3 out of 10</v>
       </c>
       <c r="I543">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="J543">
         <v>30</v>
@@ -29201,10 +29201,10 @@
         <v>No</v>
       </c>
       <c r="H544" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.6 out of 10</v>
       </c>
       <c r="I544">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J544">
         <v>30</v>
@@ -29254,10 +29254,10 @@
         <v>No</v>
       </c>
       <c r="H545" t="str">
-        <v>6.5 out of 10</v>
+        <v>1.4 out of 10</v>
       </c>
       <c r="I545">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="J545">
         <v>30</v>
@@ -29307,10 +29307,10 @@
         <v>No</v>
       </c>
       <c r="H546" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.8 out of 10</v>
       </c>
       <c r="I546">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J546">
         <v>30</v>
@@ -29360,10 +29360,10 @@
         <v>No</v>
       </c>
       <c r="H547" t="str">
-        <v>6.5 out of 10</v>
+        <v>3 out of 10</v>
       </c>
       <c r="I547">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="J547">
         <v>30</v>
@@ -29413,10 +29413,10 @@
         <v>No</v>
       </c>
       <c r="H548" t="str">
-        <v>6.5 out of 10</v>
+        <v>6.6 out of 10</v>
       </c>
       <c r="I548">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J548">
         <v>30</v>
@@ -29466,10 +29466,10 @@
         <v>No</v>
       </c>
       <c r="H549" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I549">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="J549">
         <v>30</v>
@@ -29519,10 +29519,10 @@
         <v>No</v>
       </c>
       <c r="H550" t="str">
-        <v>6.5 out of 10</v>
+        <v>7.3 out of 10</v>
       </c>
       <c r="I550">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J550">
         <v>30</v>
@@ -29572,10 +29572,10 @@
         <v>No</v>
       </c>
       <c r="H551" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.9 out of 10</v>
       </c>
       <c r="I551">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J551">
         <v>30</v>
@@ -29625,10 +29625,10 @@
         <v>No</v>
       </c>
       <c r="H552" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I552">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="J552">
         <v>30</v>
@@ -29678,10 +29678,10 @@
         <v>No</v>
       </c>
       <c r="H553" t="str">
-        <v>6.5 out of 10</v>
+        <v>2.3 out of 10</v>
       </c>
       <c r="I553">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="J553">
         <v>30</v>
@@ -29731,10 +29731,10 @@
         <v>No</v>
       </c>
       <c r="H554" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.6 out of 10</v>
       </c>
       <c r="I554">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J554">
         <v>30</v>
@@ -29784,10 +29784,10 @@
         <v>No</v>
       </c>
       <c r="H555" t="str">
-        <v>6.5 out of 10</v>
+        <v>5.4 out of 10</v>
       </c>
       <c r="I555">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J555">
         <v>30</v>
@@ -29837,10 +29837,10 @@
         <v>No</v>
       </c>
       <c r="H556" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I556">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J556">
         <v>30</v>
@@ -29890,10 +29890,10 @@
         <v>No</v>
       </c>
       <c r="H557" t="str">
-        <v>6.5 out of 10</v>
+        <v>1 out of 10</v>
       </c>
       <c r="I557">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="J557">
         <v>30</v>
@@ -29943,10 +29943,10 @@
         <v>No</v>
       </c>
       <c r="H558" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.4 out of 10</v>
       </c>
       <c r="I558">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J558">
         <v>30</v>
@@ -29996,10 +29996,10 @@
         <v>No</v>
       </c>
       <c r="H559" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.8 out of 10</v>
       </c>
       <c r="I559">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="J559">
         <v>30</v>
@@ -30049,10 +30049,10 @@
         <v>No</v>
       </c>
       <c r="H560" t="str">
-        <v>6.5 out of 10</v>
+        <v>3.4 out of 10</v>
       </c>
       <c r="I560">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="J560">
         <v>30</v>
@@ -30155,10 +30155,10 @@
         <v>No</v>
       </c>
       <c r="H562" t="str">
-        <v>6.5 out of 10</v>
+        <v>4.1 out of 10</v>
       </c>
       <c r="I562">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="J562">
         <v>30</v>
